--- a/templates/ERC000038/metadata_template_ERC000038.xlsx
+++ b/templates/ERC000038/metadata_template_ERC000038.xlsx
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="aquacultureorigin">'cv_sample'!$K$1:$K$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AF$1:$AF$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AF$1:$AF$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="samplehealthstate">'cv_sample'!$Q$1:$Q$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="633">
   <si>
     <t>alias</t>
   </si>
@@ -449,6 +449,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -539,6 +542,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1019,7 +1025,7 @@
     <t>toxin burden</t>
   </si>
   <si>
-    <t>(Recommended) Concentration of toxins in the organism at the time of sampling (Units: mg)</t>
+    <t>(Recommended) Concentration of toxins in the organism at the time of sampling (Units: kg)</t>
   </si>
   <si>
     <t>Afghanistan</t>
@@ -1235,9 +1241,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1256,6 +1259,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1457,6 +1463,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1466,9 +1475,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1508,7 +1514,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1577,6 +1583,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1652,6 +1661,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1673,6 +1685,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1718,6 +1733,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1730,6 +1748,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1739,9 +1760,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1766,6 +1784,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1826,12 +1847,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1910,7 +1931,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Mandatory) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
@@ -2437,10 +2458,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2481,10 +2502,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2532,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2528,7 +2549,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2545,7 +2566,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2562,7 +2583,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2579,7 +2600,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2596,7 +2617,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2613,7 +2634,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2630,7 +2651,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2647,7 +2668,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2664,7 +2685,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2678,7 +2699,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2692,7 +2713,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2706,7 +2727,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2720,7 +2741,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2734,7 +2755,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2748,7 +2769,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2762,7 +2783,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2776,7 +2797,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2786,8 +2807,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2798,7 +2822,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2809,7 +2833,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2820,7 +2844,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2831,7 +2855,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2842,7 +2866,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2853,7 +2877,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2864,7 +2888,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2875,7 +2899,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2886,7 +2910,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2897,7 +2921,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2908,7 +2932,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2919,7 +2943,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2930,7 +2954,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2938,7 +2962,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2946,7 +2970,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2954,7 +2978,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2962,7 +2986,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2970,7 +2994,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2978,7 +3002,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2986,7 +3010,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2994,7 +3018,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3002,7 +3026,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3010,236 +3034,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3261,27 +3290,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3301,122 +3330,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3440,210 +3469,210 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -3664,1467 +3693,1492 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="K1:AF289"/>
+  <dimension ref="K1:AF294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="11:32">
       <c r="K1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AF1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="11:32">
       <c r="K2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AF2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="11:32">
       <c r="K3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AF3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="11:32">
       <c r="AF4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="11:32">
       <c r="AF5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="11:32">
       <c r="AF6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="11:32">
       <c r="AF7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="11:32">
       <c r="AF8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="11:32">
       <c r="AF9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="11:32">
       <c r="AF10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="11:32">
       <c r="AF11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="11:32">
       <c r="AF12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="11:32">
       <c r="AF13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="11:32">
       <c r="AF14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="11:32">
       <c r="AF15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="11:32">
       <c r="AF16" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="32:32">
       <c r="AF17" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="32:32">
       <c r="AF18" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="32:32">
       <c r="AF19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="32:32">
       <c r="AF20" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="32:32">
       <c r="AF21" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="32:32">
       <c r="AF22" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="32:32">
       <c r="AF23" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="32:32">
       <c r="AF24" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="32:32">
       <c r="AF25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="32:32">
       <c r="AF26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="32:32">
       <c r="AF27" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="32:32">
       <c r="AF28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="32:32">
       <c r="AF29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="32:32">
       <c r="AF30" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="32:32">
       <c r="AF31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="32:32">
       <c r="AF32" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33" spans="32:32">
       <c r="AF33" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="32:32">
       <c r="AF34" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="32:32">
       <c r="AF35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="32:32">
       <c r="AF36" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="32:32">
       <c r="AF37" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="32:32">
       <c r="AF38" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="32:32">
       <c r="AF39" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="32:32">
       <c r="AF40" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="32:32">
       <c r="AF41" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="32:32">
       <c r="AF42" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="32:32">
       <c r="AF43" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="32:32">
       <c r="AF44" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="32:32">
       <c r="AF45" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="32:32">
       <c r="AF46" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="32:32">
       <c r="AF47" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="32:32">
       <c r="AF48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="32:32">
       <c r="AF49" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="32:32">
       <c r="AF50" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="32:32">
       <c r="AF51" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="32:32">
       <c r="AF52" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="32:32">
       <c r="AF53" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="32:32">
       <c r="AF54" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="32:32">
       <c r="AF55" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="32:32">
       <c r="AF56" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="32:32">
       <c r="AF57" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="32:32">
       <c r="AF58" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="32:32">
       <c r="AF59" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="32:32">
       <c r="AF60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="32:32">
       <c r="AF61" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="32:32">
       <c r="AF62" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="32:32">
       <c r="AF63" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64" spans="32:32">
       <c r="AF64" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="32:32">
       <c r="AF65" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="32:32">
       <c r="AF66" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="32:32">
       <c r="AF67" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="32:32">
       <c r="AF68" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="32:32">
       <c r="AF69" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="32:32">
       <c r="AF70" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="32:32">
       <c r="AF71" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="32:32">
       <c r="AF72" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="32:32">
       <c r="AF73" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="32:32">
       <c r="AF74" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="32:32">
       <c r="AF75" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="76" spans="32:32">
       <c r="AF76" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="32:32">
       <c r="AF77" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="32:32">
       <c r="AF78" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="32:32">
       <c r="AF79" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="32:32">
       <c r="AF80" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="81" spans="32:32">
       <c r="AF81" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="82" spans="32:32">
       <c r="AF82" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="32:32">
       <c r="AF83" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="84" spans="32:32">
       <c r="AF84" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="32:32">
       <c r="AF85" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="32:32">
       <c r="AF86" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="32:32">
       <c r="AF87" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="88" spans="32:32">
       <c r="AF88" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="32:32">
       <c r="AF89" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="32:32">
       <c r="AF90" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="91" spans="32:32">
       <c r="AF91" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="32:32">
       <c r="AF92" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="32:32">
       <c r="AF93" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="94" spans="32:32">
       <c r="AF94" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="32:32">
       <c r="AF95" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="32:32">
       <c r="AF96" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="32:32">
       <c r="AF97" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="32:32">
       <c r="AF98" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="32:32">
       <c r="AF99" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="32:32">
       <c r="AF100" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="32:32">
       <c r="AF101" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="102" spans="32:32">
       <c r="AF102" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="32:32">
       <c r="AF103" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="32:32">
       <c r="AF104" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="32:32">
       <c r="AF105" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="32:32">
       <c r="AF106" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="32:32">
       <c r="AF107" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="32:32">
       <c r="AF108" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="109" spans="32:32">
       <c r="AF109" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="110" spans="32:32">
       <c r="AF110" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="32:32">
       <c r="AF111" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="32:32">
       <c r="AF112" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="113" spans="32:32">
       <c r="AF113" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="114" spans="32:32">
       <c r="AF114" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="32:32">
       <c r="AF115" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="32:32">
       <c r="AF116" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="117" spans="32:32">
       <c r="AF117" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="32:32">
       <c r="AF118" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="119" spans="32:32">
       <c r="AF119" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="120" spans="32:32">
       <c r="AF120" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="32:32">
       <c r="AF121" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="122" spans="32:32">
       <c r="AF122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="32:32">
       <c r="AF123" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="124" spans="32:32">
       <c r="AF124" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="32:32">
       <c r="AF125" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="126" spans="32:32">
       <c r="AF126" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="127" spans="32:32">
       <c r="AF127" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="128" spans="32:32">
       <c r="AF128" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="129" spans="32:32">
       <c r="AF129" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="130" spans="32:32">
       <c r="AF130" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="131" spans="32:32">
       <c r="AF131" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="132" spans="32:32">
       <c r="AF132" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="133" spans="32:32">
       <c r="AF133" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="134" spans="32:32">
       <c r="AF134" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="135" spans="32:32">
       <c r="AF135" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="136" spans="32:32">
       <c r="AF136" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="137" spans="32:32">
       <c r="AF137" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="138" spans="32:32">
       <c r="AF138" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="139" spans="32:32">
       <c r="AF139" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="32:32">
       <c r="AF140" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="141" spans="32:32">
       <c r="AF141" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="142" spans="32:32">
       <c r="AF142" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="143" spans="32:32">
       <c r="AF143" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="144" spans="32:32">
       <c r="AF144" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="32:32">
       <c r="AF145" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="146" spans="32:32">
       <c r="AF146" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="147" spans="32:32">
       <c r="AF147" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="148" spans="32:32">
       <c r="AF148" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="149" spans="32:32">
       <c r="AF149" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="150" spans="32:32">
       <c r="AF150" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="151" spans="32:32">
       <c r="AF151" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="152" spans="32:32">
       <c r="AF152" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="153" spans="32:32">
       <c r="AF153" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="154" spans="32:32">
       <c r="AF154" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="155" spans="32:32">
       <c r="AF155" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="156" spans="32:32">
       <c r="AF156" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157" spans="32:32">
       <c r="AF157" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="158" spans="32:32">
       <c r="AF158" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="159" spans="32:32">
       <c r="AF159" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="160" spans="32:32">
       <c r="AF160" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="161" spans="32:32">
       <c r="AF161" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="162" spans="32:32">
       <c r="AF162" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="163" spans="32:32">
       <c r="AF163" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="164" spans="32:32">
       <c r="AF164" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="165" spans="32:32">
       <c r="AF165" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="166" spans="32:32">
       <c r="AF166" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="167" spans="32:32">
       <c r="AF167" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="168" spans="32:32">
       <c r="AF168" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="169" spans="32:32">
       <c r="AF169" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="170" spans="32:32">
       <c r="AF170" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="171" spans="32:32">
       <c r="AF171" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="172" spans="32:32">
       <c r="AF172" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="173" spans="32:32">
       <c r="AF173" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="174" spans="32:32">
       <c r="AF174" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="175" spans="32:32">
       <c r="AF175" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="176" spans="32:32">
       <c r="AF176" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="177" spans="32:32">
       <c r="AF177" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="178" spans="32:32">
       <c r="AF178" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="179" spans="32:32">
       <c r="AF179" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="180" spans="32:32">
       <c r="AF180" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="181" spans="32:32">
       <c r="AF181" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="182" spans="32:32">
       <c r="AF182" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="183" spans="32:32">
       <c r="AF183" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="184" spans="32:32">
       <c r="AF184" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="185" spans="32:32">
       <c r="AF185" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="186" spans="32:32">
       <c r="AF186" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="187" spans="32:32">
       <c r="AF187" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="188" spans="32:32">
       <c r="AF188" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="189" spans="32:32">
       <c r="AF189" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="190" spans="32:32">
       <c r="AF190" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="191" spans="32:32">
       <c r="AF191" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="192" spans="32:32">
       <c r="AF192" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="193" spans="32:32">
       <c r="AF193" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="194" spans="32:32">
       <c r="AF194" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="195" spans="32:32">
       <c r="AF195" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="196" spans="32:32">
       <c r="AF196" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="197" spans="32:32">
       <c r="AF197" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="32:32">
       <c r="AF198" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="199" spans="32:32">
       <c r="AF199" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="200" spans="32:32">
       <c r="AF200" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="201" spans="32:32">
       <c r="AF201" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="202" spans="32:32">
       <c r="AF202" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="203" spans="32:32">
       <c r="AF203" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="204" spans="32:32">
       <c r="AF204" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="205" spans="32:32">
       <c r="AF205" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="206" spans="32:32">
       <c r="AF206" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="207" spans="32:32">
       <c r="AF207" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="208" spans="32:32">
       <c r="AF208" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="209" spans="32:32">
       <c r="AF209" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="210" spans="32:32">
       <c r="AF210" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="211" spans="32:32">
       <c r="AF211" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="212" spans="32:32">
       <c r="AF212" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="213" spans="32:32">
       <c r="AF213" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="214" spans="32:32">
       <c r="AF214" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="215" spans="32:32">
       <c r="AF215" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="216" spans="32:32">
       <c r="AF216" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="217" spans="32:32">
       <c r="AF217" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="218" spans="32:32">
       <c r="AF218" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="219" spans="32:32">
       <c r="AF219" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="220" spans="32:32">
       <c r="AF220" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="221" spans="32:32">
       <c r="AF221" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="222" spans="32:32">
       <c r="AF222" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="223" spans="32:32">
       <c r="AF223" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="224" spans="32:32">
       <c r="AF224" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="225" spans="32:32">
       <c r="AF225" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="226" spans="32:32">
       <c r="AF226" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="227" spans="32:32">
       <c r="AF227" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="228" spans="32:32">
       <c r="AF228" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="229" spans="32:32">
       <c r="AF229" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="230" spans="32:32">
       <c r="AF230" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="32:32">
       <c r="AF231" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="232" spans="32:32">
       <c r="AF232" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="233" spans="32:32">
       <c r="AF233" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="234" spans="32:32">
       <c r="AF234" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="235" spans="32:32">
       <c r="AF235" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="236" spans="32:32">
       <c r="AF236" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="237" spans="32:32">
       <c r="AF237" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="238" spans="32:32">
       <c r="AF238" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="239" spans="32:32">
       <c r="AF239" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="240" spans="32:32">
       <c r="AF240" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="241" spans="32:32">
       <c r="AF241" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="242" spans="32:32">
       <c r="AF242" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="243" spans="32:32">
       <c r="AF243" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="244" spans="32:32">
       <c r="AF244" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="245" spans="32:32">
       <c r="AF245" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="246" spans="32:32">
       <c r="AF246" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="247" spans="32:32">
       <c r="AF247" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="248" spans="32:32">
       <c r="AF248" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="249" spans="32:32">
       <c r="AF249" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="250" spans="32:32">
       <c r="AF250" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="251" spans="32:32">
       <c r="AF251" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="252" spans="32:32">
       <c r="AF252" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="253" spans="32:32">
       <c r="AF253" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="254" spans="32:32">
       <c r="AF254" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="255" spans="32:32">
       <c r="AF255" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="256" spans="32:32">
       <c r="AF256" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="257" spans="32:32">
       <c r="AF257" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="258" spans="32:32">
       <c r="AF258" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="259" spans="32:32">
       <c r="AF259" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" spans="32:32">
       <c r="AF260" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="261" spans="32:32">
       <c r="AF261" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="262" spans="32:32">
       <c r="AF262" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="263" spans="32:32">
       <c r="AF263" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="264" spans="32:32">
       <c r="AF264" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="265" spans="32:32">
       <c r="AF265" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="266" spans="32:32">
       <c r="AF266" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="267" spans="32:32">
       <c r="AF267" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="268" spans="32:32">
       <c r="AF268" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="269" spans="32:32">
       <c r="AF269" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="270" spans="32:32">
       <c r="AF270" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="271" spans="32:32">
       <c r="AF271" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="272" spans="32:32">
       <c r="AF272" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="273" spans="32:32">
       <c r="AF273" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="274" spans="32:32">
       <c r="AF274" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="275" spans="32:32">
       <c r="AF275" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="276" spans="32:32">
       <c r="AF276" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="277" spans="32:32">
       <c r="AF277" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="278" spans="32:32">
       <c r="AF278" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="279" spans="32:32">
       <c r="AF279" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="280" spans="32:32">
       <c r="AF280" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="281" spans="32:32">
       <c r="AF281" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="282" spans="32:32">
       <c r="AF282" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="283" spans="32:32">
       <c r="AF283" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="284" spans="32:32">
       <c r="AF284" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="285" spans="32:32">
       <c r="AF285" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="286" spans="32:32">
       <c r="AF286" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="287" spans="32:32">
       <c r="AF287" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="288" spans="32:32">
       <c r="AF288" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="289" spans="32:32">
       <c r="AF289" t="s">
-        <v>617</v>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="290" spans="32:32">
+      <c r="AF290" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="291" spans="32:32">
+      <c r="AF291" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="292" spans="32:32">
+      <c r="AF292" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="293" spans="32:32">
+      <c r="AF293" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="294" spans="32:32">
+      <c r="AF294" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000038/metadata_template_ERC000038.xlsx
+++ b/templates/ERC000038/metadata_template_ERC000038.xlsx
@@ -17,15 +17,15 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="aquacultureorigin">'cv_sample'!$I$1:$I$3</definedName>
+    <definedName name="aquacultureorigin">'cv_sample'!$J$1:$J$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AD$1:$AD$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AE$1:$AE$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
-    <definedName name="samplehealthstate">'cv_sample'!$O$1:$O$2</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
+    <definedName name="samplehealthstate">'cv_sample'!$P$1:$P$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="631">
   <si>
     <t>alias</t>
   </si>
@@ -449,6 +449,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -539,6 +542,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -839,6 +845,12 @@
     <t>(Mandatory) Ncbi taxonomy identifier.  this is appropriate for individual organisms and some environmental samples.</t>
   </si>
   <si>
+    <t>scientific_name</t>
+  </si>
+  <si>
+    <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
     <t>sample_description</t>
   </si>
   <si>
@@ -1223,9 +1235,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1244,6 +1253,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1445,6 +1457,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1454,9 +1469,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1496,7 +1508,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1565,6 +1577,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1640,6 +1655,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1661,6 +1679,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1706,6 +1727,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1718,6 +1742,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1727,9 +1754,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1754,6 +1778,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1814,10 +1841,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2425,10 +2452,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2469,10 +2496,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2499,7 +2526,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2516,7 +2543,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2533,7 +2560,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2550,7 +2577,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2567,7 +2594,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2584,7 +2611,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2601,7 +2628,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2618,7 +2645,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2635,7 +2662,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2652,7 +2679,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2666,7 +2693,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2680,7 +2707,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2694,7 +2721,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2708,7 +2735,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2722,7 +2749,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2736,7 +2763,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2750,7 +2777,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2764,7 +2791,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2774,8 +2801,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2786,7 +2816,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2797,7 +2827,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2808,7 +2838,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2819,7 +2849,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2830,7 +2860,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2841,7 +2871,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2852,7 +2882,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2863,7 +2893,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2874,7 +2904,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2885,7 +2915,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2896,7 +2926,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2907,7 +2937,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2918,7 +2948,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2926,7 +2956,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2934,7 +2964,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2942,7 +2972,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2950,7 +2980,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2958,7 +2988,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2966,7 +2996,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2974,7 +3004,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2982,7 +3012,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -2990,7 +3020,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -2998,236 +3028,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3249,27 +3284,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3289,122 +3324,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3414,13 +3449,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33">
+    <row r="1" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3428,209 +3463,215 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>295</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>614</v>
+        <v>327</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" ht="150" customHeight="1">
+        <v>627</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>296</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>615</v>
+        <v>328</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>621</v>
+        <v>628</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
       <formula1>aquacultureorigin</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
       <formula1>samplehealthstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD3:AD101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -3640,1467 +3681,1492 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="I1:AD289"/>
+  <dimension ref="J1:AE294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="9:30">
-      <c r="I1" t="s">
-        <v>278</v>
-      </c>
-      <c r="O1" t="s">
-        <v>293</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2" spans="9:30">
-      <c r="I2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="3" spans="9:30">
-      <c r="I3" t="s">
-        <v>280</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="4" spans="9:30">
-      <c r="AD4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="5" spans="9:30">
-      <c r="AD5" t="s">
+    <row r="1" spans="10:31">
+      <c r="J1" t="s">
+        <v>282</v>
+      </c>
+      <c r="P1" t="s">
+        <v>297</v>
+      </c>
+      <c r="AE1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="9:30">
-      <c r="AD6" t="s">
+    <row r="2" spans="10:31">
+      <c r="J2" t="s">
+        <v>283</v>
+      </c>
+      <c r="P2" t="s">
+        <v>298</v>
+      </c>
+      <c r="AE2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="9:30">
-      <c r="AD7" t="s">
+    <row r="3" spans="10:31">
+      <c r="J3" t="s">
+        <v>284</v>
+      </c>
+      <c r="AE3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="8" spans="9:30">
-      <c r="AD8" t="s">
+    <row r="4" spans="10:31">
+      <c r="AE4" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="9:30">
-      <c r="AD9" t="s">
+    <row r="5" spans="10:31">
+      <c r="AE5" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="10" spans="9:30">
-      <c r="AD10" t="s">
+    <row r="6" spans="10:31">
+      <c r="AE6" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="11" spans="9:30">
-      <c r="AD11" t="s">
+    <row r="7" spans="10:31">
+      <c r="AE7" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="12" spans="9:30">
-      <c r="AD12" t="s">
+    <row r="8" spans="10:31">
+      <c r="AE8" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="13" spans="9:30">
-      <c r="AD13" t="s">
+    <row r="9" spans="10:31">
+      <c r="AE9" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="14" spans="9:30">
-      <c r="AD14" t="s">
+    <row r="10" spans="10:31">
+      <c r="AE10" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="15" spans="9:30">
-      <c r="AD15" t="s">
+    <row r="11" spans="10:31">
+      <c r="AE11" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="16" spans="9:30">
-      <c r="AD16" t="s">
+    <row r="12" spans="10:31">
+      <c r="AE12" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="30:30">
-      <c r="AD17" t="s">
+    <row r="13" spans="10:31">
+      <c r="AE13" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="18" spans="30:30">
-      <c r="AD18" t="s">
+    <row r="14" spans="10:31">
+      <c r="AE14" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="19" spans="30:30">
-      <c r="AD19" t="s">
+    <row r="15" spans="10:31">
+      <c r="AE15" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="20" spans="30:30">
-      <c r="AD20" t="s">
+    <row r="16" spans="10:31">
+      <c r="AE16" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="21" spans="30:30">
-      <c r="AD21" t="s">
+    <row r="17" spans="31:31">
+      <c r="AE17" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="22" spans="30:30">
-      <c r="AD22" t="s">
+    <row r="18" spans="31:31">
+      <c r="AE18" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="23" spans="30:30">
-      <c r="AD23" t="s">
+    <row r="19" spans="31:31">
+      <c r="AE19" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="24" spans="30:30">
-      <c r="AD24" t="s">
+    <row r="20" spans="31:31">
+      <c r="AE20" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="25" spans="30:30">
-      <c r="AD25" t="s">
+    <row r="21" spans="31:31">
+      <c r="AE21" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="26" spans="30:30">
-      <c r="AD26" t="s">
+    <row r="22" spans="31:31">
+      <c r="AE22" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="27" spans="30:30">
-      <c r="AD27" t="s">
+    <row r="23" spans="31:31">
+      <c r="AE23" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="28" spans="30:30">
-      <c r="AD28" t="s">
+    <row r="24" spans="31:31">
+      <c r="AE24" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="29" spans="30:30">
-      <c r="AD29" t="s">
+    <row r="25" spans="31:31">
+      <c r="AE25" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="30" spans="30:30">
-      <c r="AD30" t="s">
+    <row r="26" spans="31:31">
+      <c r="AE26" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="31" spans="30:30">
-      <c r="AD31" t="s">
+    <row r="27" spans="31:31">
+      <c r="AE27" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="32" spans="30:30">
-      <c r="AD32" t="s">
+    <row r="28" spans="31:31">
+      <c r="AE28" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="33" spans="30:30">
-      <c r="AD33" t="s">
+    <row r="29" spans="31:31">
+      <c r="AE29" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="34" spans="30:30">
-      <c r="AD34" t="s">
+    <row r="30" spans="31:31">
+      <c r="AE30" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="35" spans="30:30">
-      <c r="AD35" t="s">
+    <row r="31" spans="31:31">
+      <c r="AE31" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="36" spans="30:30">
-      <c r="AD36" t="s">
+    <row r="32" spans="31:31">
+      <c r="AE32" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="37" spans="30:30">
-      <c r="AD37" t="s">
+    <row r="33" spans="31:31">
+      <c r="AE33" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="38" spans="30:30">
-      <c r="AD38" t="s">
+    <row r="34" spans="31:31">
+      <c r="AE34" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="39" spans="30:30">
-      <c r="AD39" t="s">
+    <row r="35" spans="31:31">
+      <c r="AE35" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="40" spans="30:30">
-      <c r="AD40" t="s">
+    <row r="36" spans="31:31">
+      <c r="AE36" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="41" spans="30:30">
-      <c r="AD41" t="s">
+    <row r="37" spans="31:31">
+      <c r="AE37" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="42" spans="30:30">
-      <c r="AD42" t="s">
+    <row r="38" spans="31:31">
+      <c r="AE38" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="43" spans="30:30">
-      <c r="AD43" t="s">
+    <row r="39" spans="31:31">
+      <c r="AE39" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="44" spans="30:30">
-      <c r="AD44" t="s">
+    <row r="40" spans="31:31">
+      <c r="AE40" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="45" spans="30:30">
-      <c r="AD45" t="s">
+    <row r="41" spans="31:31">
+      <c r="AE41" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="46" spans="30:30">
-      <c r="AD46" t="s">
+    <row r="42" spans="31:31">
+      <c r="AE42" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="47" spans="30:30">
-      <c r="AD47" t="s">
+    <row r="43" spans="31:31">
+      <c r="AE43" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="48" spans="30:30">
-      <c r="AD48" t="s">
+    <row r="44" spans="31:31">
+      <c r="AE44" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="49" spans="30:30">
-      <c r="AD49" t="s">
+    <row r="45" spans="31:31">
+      <c r="AE45" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="50" spans="30:30">
-      <c r="AD50" t="s">
+    <row r="46" spans="31:31">
+      <c r="AE46" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="51" spans="30:30">
-      <c r="AD51" t="s">
+    <row r="47" spans="31:31">
+      <c r="AE47" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="52" spans="30:30">
-      <c r="AD52" t="s">
+    <row r="48" spans="31:31">
+      <c r="AE48" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="53" spans="30:30">
-      <c r="AD53" t="s">
+    <row r="49" spans="31:31">
+      <c r="AE49" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="54" spans="30:30">
-      <c r="AD54" t="s">
+    <row r="50" spans="31:31">
+      <c r="AE50" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="55" spans="30:30">
-      <c r="AD55" t="s">
+    <row r="51" spans="31:31">
+      <c r="AE51" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="56" spans="30:30">
-      <c r="AD56" t="s">
+    <row r="52" spans="31:31">
+      <c r="AE52" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="57" spans="30:30">
-      <c r="AD57" t="s">
+    <row r="53" spans="31:31">
+      <c r="AE53" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="58" spans="30:30">
-      <c r="AD58" t="s">
+    <row r="54" spans="31:31">
+      <c r="AE54" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="59" spans="30:30">
-      <c r="AD59" t="s">
+    <row r="55" spans="31:31">
+      <c r="AE55" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="60" spans="30:30">
-      <c r="AD60" t="s">
+    <row r="56" spans="31:31">
+      <c r="AE56" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="61" spans="30:30">
-      <c r="AD61" t="s">
+    <row r="57" spans="31:31">
+      <c r="AE57" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="62" spans="30:30">
-      <c r="AD62" t="s">
+    <row r="58" spans="31:31">
+      <c r="AE58" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="63" spans="30:30">
-      <c r="AD63" t="s">
+    <row r="59" spans="31:31">
+      <c r="AE59" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="64" spans="30:30">
-      <c r="AD64" t="s">
+    <row r="60" spans="31:31">
+      <c r="AE60" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="65" spans="30:30">
-      <c r="AD65" t="s">
+    <row r="61" spans="31:31">
+      <c r="AE61" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="66" spans="30:30">
-      <c r="AD66" t="s">
+    <row r="62" spans="31:31">
+      <c r="AE62" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="67" spans="30:30">
-      <c r="AD67" t="s">
+    <row r="63" spans="31:31">
+      <c r="AE63" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="68" spans="30:30">
-      <c r="AD68" t="s">
+    <row r="64" spans="31:31">
+      <c r="AE64" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="69" spans="30:30">
-      <c r="AD69" t="s">
+    <row r="65" spans="31:31">
+      <c r="AE65" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="70" spans="30:30">
-      <c r="AD70" t="s">
+    <row r="66" spans="31:31">
+      <c r="AE66" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="71" spans="30:30">
-      <c r="AD71" t="s">
+    <row r="67" spans="31:31">
+      <c r="AE67" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="72" spans="30:30">
-      <c r="AD72" t="s">
+    <row r="68" spans="31:31">
+      <c r="AE68" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="73" spans="30:30">
-      <c r="AD73" t="s">
+    <row r="69" spans="31:31">
+      <c r="AE69" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="74" spans="30:30">
-      <c r="AD74" t="s">
+    <row r="70" spans="31:31">
+      <c r="AE70" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="75" spans="30:30">
-      <c r="AD75" t="s">
+    <row r="71" spans="31:31">
+      <c r="AE71" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="76" spans="30:30">
-      <c r="AD76" t="s">
+    <row r="72" spans="31:31">
+      <c r="AE72" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="77" spans="30:30">
-      <c r="AD77" t="s">
+    <row r="73" spans="31:31">
+      <c r="AE73" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="78" spans="30:30">
-      <c r="AD78" t="s">
+    <row r="74" spans="31:31">
+      <c r="AE74" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="79" spans="30:30">
-      <c r="AD79" t="s">
+    <row r="75" spans="31:31">
+      <c r="AE75" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="80" spans="30:30">
-      <c r="AD80" t="s">
+    <row r="76" spans="31:31">
+      <c r="AE76" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="81" spans="30:30">
-      <c r="AD81" t="s">
+    <row r="77" spans="31:31">
+      <c r="AE77" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="82" spans="30:30">
-      <c r="AD82" t="s">
+    <row r="78" spans="31:31">
+      <c r="AE78" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="83" spans="30:30">
-      <c r="AD83" t="s">
+    <row r="79" spans="31:31">
+      <c r="AE79" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="84" spans="30:30">
-      <c r="AD84" t="s">
+    <row r="80" spans="31:31">
+      <c r="AE80" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="85" spans="30:30">
-      <c r="AD85" t="s">
+    <row r="81" spans="31:31">
+      <c r="AE81" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="86" spans="30:30">
-      <c r="AD86" t="s">
+    <row r="82" spans="31:31">
+      <c r="AE82" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="87" spans="30:30">
-      <c r="AD87" t="s">
+    <row r="83" spans="31:31">
+      <c r="AE83" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="88" spans="30:30">
-      <c r="AD88" t="s">
+    <row r="84" spans="31:31">
+      <c r="AE84" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="89" spans="30:30">
-      <c r="AD89" t="s">
+    <row r="85" spans="31:31">
+      <c r="AE85" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="90" spans="30:30">
-      <c r="AD90" t="s">
+    <row r="86" spans="31:31">
+      <c r="AE86" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="91" spans="30:30">
-      <c r="AD91" t="s">
+    <row r="87" spans="31:31">
+      <c r="AE87" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="92" spans="30:30">
-      <c r="AD92" t="s">
+    <row r="88" spans="31:31">
+      <c r="AE88" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="93" spans="30:30">
-      <c r="AD93" t="s">
+    <row r="89" spans="31:31">
+      <c r="AE89" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="94" spans="30:30">
-      <c r="AD94" t="s">
+    <row r="90" spans="31:31">
+      <c r="AE90" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="95" spans="30:30">
-      <c r="AD95" t="s">
+    <row r="91" spans="31:31">
+      <c r="AE91" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="96" spans="30:30">
-      <c r="AD96" t="s">
+    <row r="92" spans="31:31">
+      <c r="AE92" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="97" spans="30:30">
-      <c r="AD97" t="s">
+    <row r="93" spans="31:31">
+      <c r="AE93" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="98" spans="30:30">
-      <c r="AD98" t="s">
+    <row r="94" spans="31:31">
+      <c r="AE94" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="99" spans="30:30">
-      <c r="AD99" t="s">
+    <row r="95" spans="31:31">
+      <c r="AE95" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="100" spans="30:30">
-      <c r="AD100" t="s">
+    <row r="96" spans="31:31">
+      <c r="AE96" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="101" spans="30:30">
-      <c r="AD101" t="s">
+    <row r="97" spans="31:31">
+      <c r="AE97" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="102" spans="30:30">
-      <c r="AD102" t="s">
+    <row r="98" spans="31:31">
+      <c r="AE98" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="103" spans="30:30">
-      <c r="AD103" t="s">
+    <row r="99" spans="31:31">
+      <c r="AE99" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="104" spans="30:30">
-      <c r="AD104" t="s">
+    <row r="100" spans="31:31">
+      <c r="AE100" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="105" spans="30:30">
-      <c r="AD105" t="s">
+    <row r="101" spans="31:31">
+      <c r="AE101" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="106" spans="30:30">
-      <c r="AD106" t="s">
+    <row r="102" spans="31:31">
+      <c r="AE102" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="107" spans="30:30">
-      <c r="AD107" t="s">
+    <row r="103" spans="31:31">
+      <c r="AE103" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="108" spans="30:30">
-      <c r="AD108" t="s">
+    <row r="104" spans="31:31">
+      <c r="AE104" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="109" spans="30:30">
-      <c r="AD109" t="s">
+    <row r="105" spans="31:31">
+      <c r="AE105" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="110" spans="30:30">
-      <c r="AD110" t="s">
+    <row r="106" spans="31:31">
+      <c r="AE106" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="111" spans="30:30">
-      <c r="AD111" t="s">
+    <row r="107" spans="31:31">
+      <c r="AE107" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="112" spans="30:30">
-      <c r="AD112" t="s">
+    <row r="108" spans="31:31">
+      <c r="AE108" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="113" spans="30:30">
-      <c r="AD113" t="s">
+    <row r="109" spans="31:31">
+      <c r="AE109" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="114" spans="30:30">
-      <c r="AD114" t="s">
+    <row r="110" spans="31:31">
+      <c r="AE110" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="115" spans="30:30">
-      <c r="AD115" t="s">
+    <row r="111" spans="31:31">
+      <c r="AE111" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="116" spans="30:30">
-      <c r="AD116" t="s">
+    <row r="112" spans="31:31">
+      <c r="AE112" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="117" spans="30:30">
-      <c r="AD117" t="s">
+    <row r="113" spans="31:31">
+      <c r="AE113" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="118" spans="30:30">
-      <c r="AD118" t="s">
+    <row r="114" spans="31:31">
+      <c r="AE114" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="119" spans="30:30">
-      <c r="AD119" t="s">
+    <row r="115" spans="31:31">
+      <c r="AE115" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="120" spans="30:30">
-      <c r="AD120" t="s">
+    <row r="116" spans="31:31">
+      <c r="AE116" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="121" spans="30:30">
-      <c r="AD121" t="s">
+    <row r="117" spans="31:31">
+      <c r="AE117" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="122" spans="30:30">
-      <c r="AD122" t="s">
+    <row r="118" spans="31:31">
+      <c r="AE118" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="123" spans="30:30">
-      <c r="AD123" t="s">
+    <row r="119" spans="31:31">
+      <c r="AE119" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="124" spans="30:30">
-      <c r="AD124" t="s">
+    <row r="120" spans="31:31">
+      <c r="AE120" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="125" spans="30:30">
-      <c r="AD125" t="s">
+    <row r="121" spans="31:31">
+      <c r="AE121" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="126" spans="30:30">
-      <c r="AD126" t="s">
+    <row r="122" spans="31:31">
+      <c r="AE122" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="127" spans="30:30">
-      <c r="AD127" t="s">
+    <row r="123" spans="31:31">
+      <c r="AE123" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="128" spans="30:30">
-      <c r="AD128" t="s">
+    <row r="124" spans="31:31">
+      <c r="AE124" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="129" spans="30:30">
-      <c r="AD129" t="s">
+    <row r="125" spans="31:31">
+      <c r="AE125" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="130" spans="30:30">
-      <c r="AD130" t="s">
+    <row r="126" spans="31:31">
+      <c r="AE126" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="131" spans="30:30">
-      <c r="AD131" t="s">
+    <row r="127" spans="31:31">
+      <c r="AE127" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="132" spans="30:30">
-      <c r="AD132" t="s">
+    <row r="128" spans="31:31">
+      <c r="AE128" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="133" spans="30:30">
-      <c r="AD133" t="s">
+    <row r="129" spans="31:31">
+      <c r="AE129" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="134" spans="30:30">
-      <c r="AD134" t="s">
+    <row r="130" spans="31:31">
+      <c r="AE130" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="135" spans="30:30">
-      <c r="AD135" t="s">
+    <row r="131" spans="31:31">
+      <c r="AE131" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="136" spans="30:30">
-      <c r="AD136" t="s">
+    <row r="132" spans="31:31">
+      <c r="AE132" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="137" spans="30:30">
-      <c r="AD137" t="s">
+    <row r="133" spans="31:31">
+      <c r="AE133" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="138" spans="30:30">
-      <c r="AD138" t="s">
+    <row r="134" spans="31:31">
+      <c r="AE134" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="139" spans="30:30">
-      <c r="AD139" t="s">
+    <row r="135" spans="31:31">
+      <c r="AE135" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="140" spans="30:30">
-      <c r="AD140" t="s">
+    <row r="136" spans="31:31">
+      <c r="AE136" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="141" spans="30:30">
-      <c r="AD141" t="s">
+    <row r="137" spans="31:31">
+      <c r="AE137" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="142" spans="30:30">
-      <c r="AD142" t="s">
+    <row r="138" spans="31:31">
+      <c r="AE138" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="143" spans="30:30">
-      <c r="AD143" t="s">
+    <row r="139" spans="31:31">
+      <c r="AE139" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="144" spans="30:30">
-      <c r="AD144" t="s">
+    <row r="140" spans="31:31">
+      <c r="AE140" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="145" spans="30:30">
-      <c r="AD145" t="s">
+    <row r="141" spans="31:31">
+      <c r="AE141" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="146" spans="30:30">
-      <c r="AD146" t="s">
+    <row r="142" spans="31:31">
+      <c r="AE142" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="147" spans="30:30">
-      <c r="AD147" t="s">
+    <row r="143" spans="31:31">
+      <c r="AE143" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="148" spans="30:30">
-      <c r="AD148" t="s">
+    <row r="144" spans="31:31">
+      <c r="AE144" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="149" spans="30:30">
-      <c r="AD149" t="s">
+    <row r="145" spans="31:31">
+      <c r="AE145" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="150" spans="30:30">
-      <c r="AD150" t="s">
+    <row r="146" spans="31:31">
+      <c r="AE146" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="151" spans="30:30">
-      <c r="AD151" t="s">
+    <row r="147" spans="31:31">
+      <c r="AE147" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="152" spans="30:30">
-      <c r="AD152" t="s">
+    <row r="148" spans="31:31">
+      <c r="AE148" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="153" spans="30:30">
-      <c r="AD153" t="s">
+    <row r="149" spans="31:31">
+      <c r="AE149" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="154" spans="30:30">
-      <c r="AD154" t="s">
+    <row r="150" spans="31:31">
+      <c r="AE150" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="155" spans="30:30">
-      <c r="AD155" t="s">
+    <row r="151" spans="31:31">
+      <c r="AE151" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="156" spans="30:30">
-      <c r="AD156" t="s">
+    <row r="152" spans="31:31">
+      <c r="AE152" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="157" spans="30:30">
-      <c r="AD157" t="s">
+    <row r="153" spans="31:31">
+      <c r="AE153" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="158" spans="30:30">
-      <c r="AD158" t="s">
+    <row r="154" spans="31:31">
+      <c r="AE154" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="159" spans="30:30">
-      <c r="AD159" t="s">
+    <row r="155" spans="31:31">
+      <c r="AE155" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="160" spans="30:30">
-      <c r="AD160" t="s">
+    <row r="156" spans="31:31">
+      <c r="AE156" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="161" spans="30:30">
-      <c r="AD161" t="s">
+    <row r="157" spans="31:31">
+      <c r="AE157" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="162" spans="30:30">
-      <c r="AD162" t="s">
+    <row r="158" spans="31:31">
+      <c r="AE158" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="163" spans="30:30">
-      <c r="AD163" t="s">
+    <row r="159" spans="31:31">
+      <c r="AE159" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="164" spans="30:30">
-      <c r="AD164" t="s">
+    <row r="160" spans="31:31">
+      <c r="AE160" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="165" spans="30:30">
-      <c r="AD165" t="s">
+    <row r="161" spans="31:31">
+      <c r="AE161" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="166" spans="30:30">
-      <c r="AD166" t="s">
+    <row r="162" spans="31:31">
+      <c r="AE162" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="167" spans="30:30">
-      <c r="AD167" t="s">
+    <row r="163" spans="31:31">
+      <c r="AE163" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="168" spans="30:30">
-      <c r="AD168" t="s">
+    <row r="164" spans="31:31">
+      <c r="AE164" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="169" spans="30:30">
-      <c r="AD169" t="s">
+    <row r="165" spans="31:31">
+      <c r="AE165" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="170" spans="30:30">
-      <c r="AD170" t="s">
+    <row r="166" spans="31:31">
+      <c r="AE166" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="171" spans="30:30">
-      <c r="AD171" t="s">
+    <row r="167" spans="31:31">
+      <c r="AE167" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="172" spans="30:30">
-      <c r="AD172" t="s">
+    <row r="168" spans="31:31">
+      <c r="AE168" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="173" spans="30:30">
-      <c r="AD173" t="s">
+    <row r="169" spans="31:31">
+      <c r="AE169" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="174" spans="30:30">
-      <c r="AD174" t="s">
+    <row r="170" spans="31:31">
+      <c r="AE170" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="175" spans="30:30">
-      <c r="AD175" t="s">
+    <row r="171" spans="31:31">
+      <c r="AE171" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="176" spans="30:30">
-      <c r="AD176" t="s">
+    <row r="172" spans="31:31">
+      <c r="AE172" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="177" spans="30:30">
-      <c r="AD177" t="s">
+    <row r="173" spans="31:31">
+      <c r="AE173" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="178" spans="30:30">
-      <c r="AD178" t="s">
+    <row r="174" spans="31:31">
+      <c r="AE174" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="179" spans="30:30">
-      <c r="AD179" t="s">
+    <row r="175" spans="31:31">
+      <c r="AE175" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="180" spans="30:30">
-      <c r="AD180" t="s">
+    <row r="176" spans="31:31">
+      <c r="AE176" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="181" spans="30:30">
-      <c r="AD181" t="s">
+    <row r="177" spans="31:31">
+      <c r="AE177" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="182" spans="30:30">
-      <c r="AD182" t="s">
+    <row r="178" spans="31:31">
+      <c r="AE178" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="183" spans="30:30">
-      <c r="AD183" t="s">
+    <row r="179" spans="31:31">
+      <c r="AE179" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="184" spans="30:30">
-      <c r="AD184" t="s">
+    <row r="180" spans="31:31">
+      <c r="AE180" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="185" spans="30:30">
-      <c r="AD185" t="s">
+    <row r="181" spans="31:31">
+      <c r="AE181" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="186" spans="30:30">
-      <c r="AD186" t="s">
+    <row r="182" spans="31:31">
+      <c r="AE182" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="187" spans="30:30">
-      <c r="AD187" t="s">
+    <row r="183" spans="31:31">
+      <c r="AE183" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="188" spans="30:30">
-      <c r="AD188" t="s">
+    <row r="184" spans="31:31">
+      <c r="AE184" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="189" spans="30:30">
-      <c r="AD189" t="s">
+    <row r="185" spans="31:31">
+      <c r="AE185" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="190" spans="30:30">
-      <c r="AD190" t="s">
+    <row r="186" spans="31:31">
+      <c r="AE186" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="191" spans="30:30">
-      <c r="AD191" t="s">
+    <row r="187" spans="31:31">
+      <c r="AE187" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="192" spans="30:30">
-      <c r="AD192" t="s">
+    <row r="188" spans="31:31">
+      <c r="AE188" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="193" spans="30:30">
-      <c r="AD193" t="s">
+    <row r="189" spans="31:31">
+      <c r="AE189" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="194" spans="30:30">
-      <c r="AD194" t="s">
+    <row r="190" spans="31:31">
+      <c r="AE190" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="195" spans="30:30">
-      <c r="AD195" t="s">
+    <row r="191" spans="31:31">
+      <c r="AE191" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="196" spans="30:30">
-      <c r="AD196" t="s">
+    <row r="192" spans="31:31">
+      <c r="AE192" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="197" spans="30:30">
-      <c r="AD197" t="s">
+    <row r="193" spans="31:31">
+      <c r="AE193" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="198" spans="30:30">
-      <c r="AD198" t="s">
+    <row r="194" spans="31:31">
+      <c r="AE194" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="199" spans="30:30">
-      <c r="AD199" t="s">
+    <row r="195" spans="31:31">
+      <c r="AE195" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="200" spans="30:30">
-      <c r="AD200" t="s">
+    <row r="196" spans="31:31">
+      <c r="AE196" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="201" spans="30:30">
-      <c r="AD201" t="s">
+    <row r="197" spans="31:31">
+      <c r="AE197" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="202" spans="30:30">
-      <c r="AD202" t="s">
+    <row r="198" spans="31:31">
+      <c r="AE198" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="203" spans="30:30">
-      <c r="AD203" t="s">
+    <row r="199" spans="31:31">
+      <c r="AE199" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="204" spans="30:30">
-      <c r="AD204" t="s">
+    <row r="200" spans="31:31">
+      <c r="AE200" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="205" spans="30:30">
-      <c r="AD205" t="s">
+    <row r="201" spans="31:31">
+      <c r="AE201" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="206" spans="30:30">
-      <c r="AD206" t="s">
+    <row r="202" spans="31:31">
+      <c r="AE202" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="207" spans="30:30">
-      <c r="AD207" t="s">
+    <row r="203" spans="31:31">
+      <c r="AE203" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="208" spans="30:30">
-      <c r="AD208" t="s">
+    <row r="204" spans="31:31">
+      <c r="AE204" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="209" spans="30:30">
-      <c r="AD209" t="s">
+    <row r="205" spans="31:31">
+      <c r="AE205" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="210" spans="30:30">
-      <c r="AD210" t="s">
+    <row r="206" spans="31:31">
+      <c r="AE206" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="211" spans="30:30">
-      <c r="AD211" t="s">
+    <row r="207" spans="31:31">
+      <c r="AE207" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="212" spans="30:30">
-      <c r="AD212" t="s">
+    <row r="208" spans="31:31">
+      <c r="AE208" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="213" spans="30:30">
-      <c r="AD213" t="s">
+    <row r="209" spans="31:31">
+      <c r="AE209" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="214" spans="30:30">
-      <c r="AD214" t="s">
+    <row r="210" spans="31:31">
+      <c r="AE210" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="215" spans="30:30">
-      <c r="AD215" t="s">
+    <row r="211" spans="31:31">
+      <c r="AE211" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="216" spans="30:30">
-      <c r="AD216" t="s">
+    <row r="212" spans="31:31">
+      <c r="AE212" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="217" spans="30:30">
-      <c r="AD217" t="s">
+    <row r="213" spans="31:31">
+      <c r="AE213" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="218" spans="30:30">
-      <c r="AD218" t="s">
+    <row r="214" spans="31:31">
+      <c r="AE214" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="219" spans="30:30">
-      <c r="AD219" t="s">
+    <row r="215" spans="31:31">
+      <c r="AE215" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="220" spans="30:30">
-      <c r="AD220" t="s">
+    <row r="216" spans="31:31">
+      <c r="AE216" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="221" spans="30:30">
-      <c r="AD221" t="s">
+    <row r="217" spans="31:31">
+      <c r="AE217" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="222" spans="30:30">
-      <c r="AD222" t="s">
+    <row r="218" spans="31:31">
+      <c r="AE218" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="223" spans="30:30">
-      <c r="AD223" t="s">
+    <row r="219" spans="31:31">
+      <c r="AE219" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="224" spans="30:30">
-      <c r="AD224" t="s">
+    <row r="220" spans="31:31">
+      <c r="AE220" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="225" spans="30:30">
-      <c r="AD225" t="s">
+    <row r="221" spans="31:31">
+      <c r="AE221" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="226" spans="30:30">
-      <c r="AD226" t="s">
+    <row r="222" spans="31:31">
+      <c r="AE222" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="227" spans="30:30">
-      <c r="AD227" t="s">
+    <row r="223" spans="31:31">
+      <c r="AE223" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="228" spans="30:30">
-      <c r="AD228" t="s">
+    <row r="224" spans="31:31">
+      <c r="AE224" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="229" spans="30:30">
-      <c r="AD229" t="s">
+    <row r="225" spans="31:31">
+      <c r="AE225" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="230" spans="30:30">
-      <c r="AD230" t="s">
+    <row r="226" spans="31:31">
+      <c r="AE226" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="231" spans="30:30">
-      <c r="AD231" t="s">
+    <row r="227" spans="31:31">
+      <c r="AE227" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="232" spans="30:30">
-      <c r="AD232" t="s">
+    <row r="228" spans="31:31">
+      <c r="AE228" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="233" spans="30:30">
-      <c r="AD233" t="s">
+    <row r="229" spans="31:31">
+      <c r="AE229" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="234" spans="30:30">
-      <c r="AD234" t="s">
+    <row r="230" spans="31:31">
+      <c r="AE230" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="235" spans="30:30">
-      <c r="AD235" t="s">
+    <row r="231" spans="31:31">
+      <c r="AE231" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="236" spans="30:30">
-      <c r="AD236" t="s">
+    <row r="232" spans="31:31">
+      <c r="AE232" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="237" spans="30:30">
-      <c r="AD237" t="s">
+    <row r="233" spans="31:31">
+      <c r="AE233" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="238" spans="30:30">
-      <c r="AD238" t="s">
+    <row r="234" spans="31:31">
+      <c r="AE234" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="239" spans="30:30">
-      <c r="AD239" t="s">
+    <row r="235" spans="31:31">
+      <c r="AE235" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="240" spans="30:30">
-      <c r="AD240" t="s">
+    <row r="236" spans="31:31">
+      <c r="AE236" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="241" spans="30:30">
-      <c r="AD241" t="s">
+    <row r="237" spans="31:31">
+      <c r="AE237" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="242" spans="30:30">
-      <c r="AD242" t="s">
+    <row r="238" spans="31:31">
+      <c r="AE238" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="243" spans="30:30">
-      <c r="AD243" t="s">
+    <row r="239" spans="31:31">
+      <c r="AE239" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="244" spans="30:30">
-      <c r="AD244" t="s">
+    <row r="240" spans="31:31">
+      <c r="AE240" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="245" spans="30:30">
-      <c r="AD245" t="s">
+    <row r="241" spans="31:31">
+      <c r="AE241" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="246" spans="30:30">
-      <c r="AD246" t="s">
+    <row r="242" spans="31:31">
+      <c r="AE242" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="247" spans="30:30">
-      <c r="AD247" t="s">
+    <row r="243" spans="31:31">
+      <c r="AE243" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="248" spans="30:30">
-      <c r="AD248" t="s">
+    <row r="244" spans="31:31">
+      <c r="AE244" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="249" spans="30:30">
-      <c r="AD249" t="s">
+    <row r="245" spans="31:31">
+      <c r="AE245" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="250" spans="30:30">
-      <c r="AD250" t="s">
+    <row r="246" spans="31:31">
+      <c r="AE246" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="251" spans="30:30">
-      <c r="AD251" t="s">
+    <row r="247" spans="31:31">
+      <c r="AE247" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="252" spans="30:30">
-      <c r="AD252" t="s">
+    <row r="248" spans="31:31">
+      <c r="AE248" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="253" spans="30:30">
-      <c r="AD253" t="s">
+    <row r="249" spans="31:31">
+      <c r="AE249" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="254" spans="30:30">
-      <c r="AD254" t="s">
+    <row r="250" spans="31:31">
+      <c r="AE250" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="255" spans="30:30">
-      <c r="AD255" t="s">
+    <row r="251" spans="31:31">
+      <c r="AE251" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="256" spans="30:30">
-      <c r="AD256" t="s">
+    <row r="252" spans="31:31">
+      <c r="AE252" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="257" spans="30:30">
-      <c r="AD257" t="s">
+    <row r="253" spans="31:31">
+      <c r="AE253" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="258" spans="30:30">
-      <c r="AD258" t="s">
+    <row r="254" spans="31:31">
+      <c r="AE254" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="259" spans="30:30">
-      <c r="AD259" t="s">
+    <row r="255" spans="31:31">
+      <c r="AE255" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="260" spans="30:30">
-      <c r="AD260" t="s">
+    <row r="256" spans="31:31">
+      <c r="AE256" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="261" spans="30:30">
-      <c r="AD261" t="s">
+    <row r="257" spans="31:31">
+      <c r="AE257" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="262" spans="30:30">
-      <c r="AD262" t="s">
+    <row r="258" spans="31:31">
+      <c r="AE258" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="263" spans="30:30">
-      <c r="AD263" t="s">
+    <row r="259" spans="31:31">
+      <c r="AE259" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="264" spans="30:30">
-      <c r="AD264" t="s">
+    <row r="260" spans="31:31">
+      <c r="AE260" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="265" spans="30:30">
-      <c r="AD265" t="s">
+    <row r="261" spans="31:31">
+      <c r="AE261" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="266" spans="30:30">
-      <c r="AD266" t="s">
+    <row r="262" spans="31:31">
+      <c r="AE262" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="267" spans="30:30">
-      <c r="AD267" t="s">
+    <row r="263" spans="31:31">
+      <c r="AE263" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="268" spans="30:30">
-      <c r="AD268" t="s">
+    <row r="264" spans="31:31">
+      <c r="AE264" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="269" spans="30:30">
-      <c r="AD269" t="s">
+    <row r="265" spans="31:31">
+      <c r="AE265" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="270" spans="30:30">
-      <c r="AD270" t="s">
+    <row r="266" spans="31:31">
+      <c r="AE266" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="271" spans="30:30">
-      <c r="AD271" t="s">
+    <row r="267" spans="31:31">
+      <c r="AE267" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="272" spans="30:30">
-      <c r="AD272" t="s">
+    <row r="268" spans="31:31">
+      <c r="AE268" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="273" spans="30:30">
-      <c r="AD273" t="s">
+    <row r="269" spans="31:31">
+      <c r="AE269" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="274" spans="30:30">
-      <c r="AD274" t="s">
+    <row r="270" spans="31:31">
+      <c r="AE270" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="275" spans="30:30">
-      <c r="AD275" t="s">
+    <row r="271" spans="31:31">
+      <c r="AE271" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="276" spans="30:30">
-      <c r="AD276" t="s">
+    <row r="272" spans="31:31">
+      <c r="AE272" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="277" spans="30:30">
-      <c r="AD277" t="s">
+    <row r="273" spans="31:31">
+      <c r="AE273" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="278" spans="30:30">
-      <c r="AD278" t="s">
+    <row r="274" spans="31:31">
+      <c r="AE274" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="279" spans="30:30">
-      <c r="AD279" t="s">
+    <row r="275" spans="31:31">
+      <c r="AE275" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="280" spans="30:30">
-      <c r="AD280" t="s">
+    <row r="276" spans="31:31">
+      <c r="AE276" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="281" spans="30:30">
-      <c r="AD281" t="s">
+    <row r="277" spans="31:31">
+      <c r="AE277" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="282" spans="30:30">
-      <c r="AD282" t="s">
+    <row r="278" spans="31:31">
+      <c r="AE278" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="283" spans="30:30">
-      <c r="AD283" t="s">
+    <row r="279" spans="31:31">
+      <c r="AE279" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="284" spans="30:30">
-      <c r="AD284" t="s">
+    <row r="280" spans="31:31">
+      <c r="AE280" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="285" spans="30:30">
-      <c r="AD285" t="s">
+    <row r="281" spans="31:31">
+      <c r="AE281" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="286" spans="30:30">
-      <c r="AD286" t="s">
+    <row r="282" spans="31:31">
+      <c r="AE282" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="287" spans="30:30">
-      <c r="AD287" t="s">
+    <row r="283" spans="31:31">
+      <c r="AE283" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="288" spans="30:30">
-      <c r="AD288" t="s">
+    <row r="284" spans="31:31">
+      <c r="AE284" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="289" spans="30:30">
-      <c r="AD289" t="s">
+    <row r="285" spans="31:31">
+      <c r="AE285" t="s">
         <v>613</v>
+      </c>
+    </row>
+    <row r="286" spans="31:31">
+      <c r="AE286" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="287" spans="31:31">
+      <c r="AE287" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="288" spans="31:31">
+      <c r="AE288" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="289" spans="31:31">
+      <c r="AE289" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="290" spans="31:31">
+      <c r="AE290" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="291" spans="31:31">
+      <c r="AE291" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="292" spans="31:31">
+      <c r="AE292" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="293" spans="31:31">
+      <c r="AE293" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="294" spans="31:31">
+      <c r="AE294" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000038/metadata_template_ERC000038.xlsx
+++ b/templates/ERC000038/metadata_template_ERC000038.xlsx
@@ -17,15 +17,15 @@
     <sheet name="cv_sample" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="aquacultureorigin">'cv_sample'!$J$1:$J$3</definedName>
+    <definedName name="aquacultureorigin">'cv_sample'!$K$1:$K$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AE$1:$AE$294</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AF$1:$AF$294</definedName>
     <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
     <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
-    <definedName name="samplehealthstate">'cv_sample'!$P$1:$P$2</definedName>
+    <definedName name="samplehealthstate">'cv_sample'!$Q$1:$Q$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="633">
   <si>
     <t>alias</t>
   </si>
@@ -849,6 +849,12 @@
   </si>
   <si>
     <t>(Optional) Scientific name of sample that distinguishes its taxonomy.  please use a name or synonym that is tracked in the insdc taxonomy database. also, this field can be used to confirm the taxon_id setting.</t>
+  </si>
+  <si>
+    <t>common_name</t>
+  </si>
+  <si>
+    <t>(Optional) Genbank common name of the organism.  examples: human, mouse.</t>
   </si>
   <si>
     <t>sample_description</t>
@@ -3449,13 +3455,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="301" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3484,7 +3490,7 @@
         <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>287</v>
@@ -3502,7 +3508,7 @@
         <v>295</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>301</v>
@@ -3547,7 +3553,7 @@
         <v>327</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>623</v>
+        <v>329</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>625</v>
@@ -3558,8 +3564,11 @@
       <c r="AH1" s="1" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" ht="150" customHeight="1">
+      <c r="AI1" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>266</v>
       </c>
@@ -3588,7 +3597,7 @@
         <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>288</v>
@@ -3606,7 +3615,7 @@
         <v>296</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>302</v>
@@ -3651,7 +3660,7 @@
         <v>328</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>624</v>
+        <v>330</v>
       </c>
       <c r="AF2" s="2" t="s">
         <v>626</v>
@@ -3662,16 +3671,19 @@
       <c r="AH2" s="2" t="s">
         <v>630</v>
       </c>
+      <c r="AI2" s="2" t="s">
+        <v>632</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K101">
       <formula1>aquacultureorigin</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q101">
       <formula1>samplehealthstate</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE3:AE101">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF3:AF101">
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
   </dataValidations>
@@ -3681,1492 +3693,1492 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="J1:AE294"/>
+  <dimension ref="K1:AF294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="10:31">
-      <c r="J1" t="s">
-        <v>282</v>
-      </c>
-      <c r="P1" t="s">
-        <v>297</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2" spans="10:31">
-      <c r="J2" t="s">
-        <v>283</v>
-      </c>
-      <c r="P2" t="s">
-        <v>298</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="3" spans="10:31">
-      <c r="J3" t="s">
+    <row r="1" spans="11:32">
+      <c r="K1" t="s">
         <v>284</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="Q1" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF1" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="4" spans="10:31">
-      <c r="AE4" t="s">
+    <row r="2" spans="11:32">
+      <c r="K2" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>300</v>
+      </c>
+      <c r="AF2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="10:31">
-      <c r="AE5" t="s">
+    <row r="3" spans="11:32">
+      <c r="K3" t="s">
+        <v>286</v>
+      </c>
+      <c r="AF3" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="10:31">
-      <c r="AE6" t="s">
+    <row r="4" spans="11:32">
+      <c r="AF4" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="7" spans="10:31">
-      <c r="AE7" t="s">
+    <row r="5" spans="11:32">
+      <c r="AF5" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="10:31">
-      <c r="AE8" t="s">
+    <row r="6" spans="11:32">
+      <c r="AF6" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="9" spans="10:31">
-      <c r="AE9" t="s">
+    <row r="7" spans="11:32">
+      <c r="AF7" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="10:31">
-      <c r="AE10" t="s">
+    <row r="8" spans="11:32">
+      <c r="AF8" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="10:31">
-      <c r="AE11" t="s">
+    <row r="9" spans="11:32">
+      <c r="AF9" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="10:31">
-      <c r="AE12" t="s">
+    <row r="10" spans="11:32">
+      <c r="AF10" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="10:31">
-      <c r="AE13" t="s">
+    <row r="11" spans="11:32">
+      <c r="AF11" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="14" spans="10:31">
-      <c r="AE14" t="s">
+    <row r="12" spans="11:32">
+      <c r="AF12" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="15" spans="10:31">
-      <c r="AE15" t="s">
+    <row r="13" spans="11:32">
+      <c r="AF13" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="16" spans="10:31">
-      <c r="AE16" t="s">
+    <row r="14" spans="11:32">
+      <c r="AF14" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="17" spans="31:31">
-      <c r="AE17" t="s">
+    <row r="15" spans="11:32">
+      <c r="AF15" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="18" spans="31:31">
-      <c r="AE18" t="s">
+    <row r="16" spans="11:32">
+      <c r="AF16" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="19" spans="31:31">
-      <c r="AE19" t="s">
+    <row r="17" spans="32:32">
+      <c r="AF17" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="20" spans="31:31">
-      <c r="AE20" t="s">
+    <row r="18" spans="32:32">
+      <c r="AF18" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="21" spans="31:31">
-      <c r="AE21" t="s">
+    <row r="19" spans="32:32">
+      <c r="AF19" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="22" spans="31:31">
-      <c r="AE22" t="s">
+    <row r="20" spans="32:32">
+      <c r="AF20" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="23" spans="31:31">
-      <c r="AE23" t="s">
+    <row r="21" spans="32:32">
+      <c r="AF21" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="24" spans="31:31">
-      <c r="AE24" t="s">
+    <row r="22" spans="32:32">
+      <c r="AF22" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="25" spans="31:31">
-      <c r="AE25" t="s">
+    <row r="23" spans="32:32">
+      <c r="AF23" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="26" spans="31:31">
-      <c r="AE26" t="s">
+    <row r="24" spans="32:32">
+      <c r="AF24" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="27" spans="31:31">
-      <c r="AE27" t="s">
+    <row r="25" spans="32:32">
+      <c r="AF25" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="28" spans="31:31">
-      <c r="AE28" t="s">
+    <row r="26" spans="32:32">
+      <c r="AF26" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="29" spans="31:31">
-      <c r="AE29" t="s">
+    <row r="27" spans="32:32">
+      <c r="AF27" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="30" spans="31:31">
-      <c r="AE30" t="s">
+    <row r="28" spans="32:32">
+      <c r="AF28" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="31" spans="31:31">
-      <c r="AE31" t="s">
+    <row r="29" spans="32:32">
+      <c r="AF29" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="32" spans="31:31">
-      <c r="AE32" t="s">
+    <row r="30" spans="32:32">
+      <c r="AF30" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="33" spans="31:31">
-      <c r="AE33" t="s">
+    <row r="31" spans="32:32">
+      <c r="AF31" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="34" spans="31:31">
-      <c r="AE34" t="s">
+    <row r="32" spans="32:32">
+      <c r="AF32" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="35" spans="31:31">
-      <c r="AE35" t="s">
+    <row r="33" spans="32:32">
+      <c r="AF33" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="36" spans="31:31">
-      <c r="AE36" t="s">
+    <row r="34" spans="32:32">
+      <c r="AF34" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="37" spans="31:31">
-      <c r="AE37" t="s">
+    <row r="35" spans="32:32">
+      <c r="AF35" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="38" spans="31:31">
-      <c r="AE38" t="s">
+    <row r="36" spans="32:32">
+      <c r="AF36" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="39" spans="31:31">
-      <c r="AE39" t="s">
+    <row r="37" spans="32:32">
+      <c r="AF37" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="40" spans="31:31">
-      <c r="AE40" t="s">
+    <row r="38" spans="32:32">
+      <c r="AF38" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="41" spans="31:31">
-      <c r="AE41" t="s">
+    <row r="39" spans="32:32">
+      <c r="AF39" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="42" spans="31:31">
-      <c r="AE42" t="s">
+    <row r="40" spans="32:32">
+      <c r="AF40" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="43" spans="31:31">
-      <c r="AE43" t="s">
+    <row r="41" spans="32:32">
+      <c r="AF41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="44" spans="31:31">
-      <c r="AE44" t="s">
+    <row r="42" spans="32:32">
+      <c r="AF42" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="45" spans="31:31">
-      <c r="AE45" t="s">
+    <row r="43" spans="32:32">
+      <c r="AF43" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="46" spans="31:31">
-      <c r="AE46" t="s">
+    <row r="44" spans="32:32">
+      <c r="AF44" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="47" spans="31:31">
-      <c r="AE47" t="s">
+    <row r="45" spans="32:32">
+      <c r="AF45" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="48" spans="31:31">
-      <c r="AE48" t="s">
+    <row r="46" spans="32:32">
+      <c r="AF46" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="49" spans="31:31">
-      <c r="AE49" t="s">
+    <row r="47" spans="32:32">
+      <c r="AF47" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="50" spans="31:31">
-      <c r="AE50" t="s">
+    <row r="48" spans="32:32">
+      <c r="AF48" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="51" spans="31:31">
-      <c r="AE51" t="s">
+    <row r="49" spans="32:32">
+      <c r="AF49" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="52" spans="31:31">
-      <c r="AE52" t="s">
+    <row r="50" spans="32:32">
+      <c r="AF50" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="53" spans="31:31">
-      <c r="AE53" t="s">
+    <row r="51" spans="32:32">
+      <c r="AF51" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="54" spans="31:31">
-      <c r="AE54" t="s">
+    <row r="52" spans="32:32">
+      <c r="AF52" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="55" spans="31:31">
-      <c r="AE55" t="s">
+    <row r="53" spans="32:32">
+      <c r="AF53" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="56" spans="31:31">
-      <c r="AE56" t="s">
+    <row r="54" spans="32:32">
+      <c r="AF54" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="57" spans="31:31">
-      <c r="AE57" t="s">
+    <row r="55" spans="32:32">
+      <c r="AF55" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="58" spans="31:31">
-      <c r="AE58" t="s">
+    <row r="56" spans="32:32">
+      <c r="AF56" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="59" spans="31:31">
-      <c r="AE59" t="s">
+    <row r="57" spans="32:32">
+      <c r="AF57" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="60" spans="31:31">
-      <c r="AE60" t="s">
+    <row r="58" spans="32:32">
+      <c r="AF58" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="61" spans="31:31">
-      <c r="AE61" t="s">
+    <row r="59" spans="32:32">
+      <c r="AF59" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="62" spans="31:31">
-      <c r="AE62" t="s">
+    <row r="60" spans="32:32">
+      <c r="AF60" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="31:31">
-      <c r="AE63" t="s">
+    <row r="61" spans="32:32">
+      <c r="AF61" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="64" spans="31:31">
-      <c r="AE64" t="s">
+    <row r="62" spans="32:32">
+      <c r="AF62" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="65" spans="31:31">
-      <c r="AE65" t="s">
+    <row r="63" spans="32:32">
+      <c r="AF63" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="66" spans="31:31">
-      <c r="AE66" t="s">
+    <row r="64" spans="32:32">
+      <c r="AF64" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="67" spans="31:31">
-      <c r="AE67" t="s">
+    <row r="65" spans="32:32">
+      <c r="AF65" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="68" spans="31:31">
-      <c r="AE68" t="s">
+    <row r="66" spans="32:32">
+      <c r="AF66" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="69" spans="31:31">
-      <c r="AE69" t="s">
+    <row r="67" spans="32:32">
+      <c r="AF67" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="70" spans="31:31">
-      <c r="AE70" t="s">
+    <row r="68" spans="32:32">
+      <c r="AF68" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="71" spans="31:31">
-      <c r="AE71" t="s">
+    <row r="69" spans="32:32">
+      <c r="AF69" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="72" spans="31:31">
-      <c r="AE72" t="s">
+    <row r="70" spans="32:32">
+      <c r="AF70" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="73" spans="31:31">
-      <c r="AE73" t="s">
+    <row r="71" spans="32:32">
+      <c r="AF71" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="74" spans="31:31">
-      <c r="AE74" t="s">
+    <row r="72" spans="32:32">
+      <c r="AF72" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="75" spans="31:31">
-      <c r="AE75" t="s">
+    <row r="73" spans="32:32">
+      <c r="AF73" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="76" spans="31:31">
-      <c r="AE76" t="s">
+    <row r="74" spans="32:32">
+      <c r="AF74" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="77" spans="31:31">
-      <c r="AE77" t="s">
+    <row r="75" spans="32:32">
+      <c r="AF75" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="78" spans="31:31">
-      <c r="AE78" t="s">
+    <row r="76" spans="32:32">
+      <c r="AF76" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="79" spans="31:31">
-      <c r="AE79" t="s">
+    <row r="77" spans="32:32">
+      <c r="AF77" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="80" spans="31:31">
-      <c r="AE80" t="s">
+    <row r="78" spans="32:32">
+      <c r="AF78" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="81" spans="31:31">
-      <c r="AE81" t="s">
+    <row r="79" spans="32:32">
+      <c r="AF79" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="82" spans="31:31">
-      <c r="AE82" t="s">
+    <row r="80" spans="32:32">
+      <c r="AF80" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="83" spans="31:31">
-      <c r="AE83" t="s">
+    <row r="81" spans="32:32">
+      <c r="AF81" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="84" spans="31:31">
-      <c r="AE84" t="s">
+    <row r="82" spans="32:32">
+      <c r="AF82" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="85" spans="31:31">
-      <c r="AE85" t="s">
+    <row r="83" spans="32:32">
+      <c r="AF83" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="86" spans="31:31">
-      <c r="AE86" t="s">
+    <row r="84" spans="32:32">
+      <c r="AF84" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="87" spans="31:31">
-      <c r="AE87" t="s">
+    <row r="85" spans="32:32">
+      <c r="AF85" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="88" spans="31:31">
-      <c r="AE88" t="s">
+    <row r="86" spans="32:32">
+      <c r="AF86" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="89" spans="31:31">
-      <c r="AE89" t="s">
+    <row r="87" spans="32:32">
+      <c r="AF87" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="90" spans="31:31">
-      <c r="AE90" t="s">
+    <row r="88" spans="32:32">
+      <c r="AF88" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="91" spans="31:31">
-      <c r="AE91" t="s">
+    <row r="89" spans="32:32">
+      <c r="AF89" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="92" spans="31:31">
-      <c r="AE92" t="s">
+    <row r="90" spans="32:32">
+      <c r="AF90" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="93" spans="31:31">
-      <c r="AE93" t="s">
+    <row r="91" spans="32:32">
+      <c r="AF91" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="94" spans="31:31">
-      <c r="AE94" t="s">
+    <row r="92" spans="32:32">
+      <c r="AF92" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="95" spans="31:31">
-      <c r="AE95" t="s">
+    <row r="93" spans="32:32">
+      <c r="AF93" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="96" spans="31:31">
-      <c r="AE96" t="s">
+    <row r="94" spans="32:32">
+      <c r="AF94" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="97" spans="31:31">
-      <c r="AE97" t="s">
+    <row r="95" spans="32:32">
+      <c r="AF95" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="98" spans="31:31">
-      <c r="AE98" t="s">
+    <row r="96" spans="32:32">
+      <c r="AF96" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="99" spans="31:31">
-      <c r="AE99" t="s">
+    <row r="97" spans="32:32">
+      <c r="AF97" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="100" spans="31:31">
-      <c r="AE100" t="s">
+    <row r="98" spans="32:32">
+      <c r="AF98" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="101" spans="31:31">
-      <c r="AE101" t="s">
+    <row r="99" spans="32:32">
+      <c r="AF99" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="102" spans="31:31">
-      <c r="AE102" t="s">
+    <row r="100" spans="32:32">
+      <c r="AF100" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="103" spans="31:31">
-      <c r="AE103" t="s">
+    <row r="101" spans="32:32">
+      <c r="AF101" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="104" spans="31:31">
-      <c r="AE104" t="s">
+    <row r="102" spans="32:32">
+      <c r="AF102" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="105" spans="31:31">
-      <c r="AE105" t="s">
+    <row r="103" spans="32:32">
+      <c r="AF103" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="106" spans="31:31">
-      <c r="AE106" t="s">
+    <row r="104" spans="32:32">
+      <c r="AF104" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="107" spans="31:31">
-      <c r="AE107" t="s">
+    <row r="105" spans="32:32">
+      <c r="AF105" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="108" spans="31:31">
-      <c r="AE108" t="s">
+    <row r="106" spans="32:32">
+      <c r="AF106" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="109" spans="31:31">
-      <c r="AE109" t="s">
+    <row r="107" spans="32:32">
+      <c r="AF107" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="110" spans="31:31">
-      <c r="AE110" t="s">
+    <row r="108" spans="32:32">
+      <c r="AF108" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="111" spans="31:31">
-      <c r="AE111" t="s">
+    <row r="109" spans="32:32">
+      <c r="AF109" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="112" spans="31:31">
-      <c r="AE112" t="s">
+    <row r="110" spans="32:32">
+      <c r="AF110" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="113" spans="31:31">
-      <c r="AE113" t="s">
+    <row r="111" spans="32:32">
+      <c r="AF111" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="114" spans="31:31">
-      <c r="AE114" t="s">
+    <row r="112" spans="32:32">
+      <c r="AF112" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="115" spans="31:31">
-      <c r="AE115" t="s">
+    <row r="113" spans="32:32">
+      <c r="AF113" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="116" spans="31:31">
-      <c r="AE116" t="s">
+    <row r="114" spans="32:32">
+      <c r="AF114" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="117" spans="31:31">
-      <c r="AE117" t="s">
+    <row r="115" spans="32:32">
+      <c r="AF115" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="118" spans="31:31">
-      <c r="AE118" t="s">
+    <row r="116" spans="32:32">
+      <c r="AF116" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="31:31">
-      <c r="AE119" t="s">
+    <row r="117" spans="32:32">
+      <c r="AF117" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="120" spans="31:31">
-      <c r="AE120" t="s">
+    <row r="118" spans="32:32">
+      <c r="AF118" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="121" spans="31:31">
-      <c r="AE121" t="s">
+    <row r="119" spans="32:32">
+      <c r="AF119" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="122" spans="31:31">
-      <c r="AE122" t="s">
+    <row r="120" spans="32:32">
+      <c r="AF120" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="123" spans="31:31">
-      <c r="AE123" t="s">
+    <row r="121" spans="32:32">
+      <c r="AF121" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="124" spans="31:31">
-      <c r="AE124" t="s">
+    <row r="122" spans="32:32">
+      <c r="AF122" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="125" spans="31:31">
-      <c r="AE125" t="s">
+    <row r="123" spans="32:32">
+      <c r="AF123" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="126" spans="31:31">
-      <c r="AE126" t="s">
+    <row r="124" spans="32:32">
+      <c r="AF124" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="127" spans="31:31">
-      <c r="AE127" t="s">
+    <row r="125" spans="32:32">
+      <c r="AF125" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="128" spans="31:31">
-      <c r="AE128" t="s">
+    <row r="126" spans="32:32">
+      <c r="AF126" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="129" spans="31:31">
-      <c r="AE129" t="s">
+    <row r="127" spans="32:32">
+      <c r="AF127" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="130" spans="31:31">
-      <c r="AE130" t="s">
+    <row r="128" spans="32:32">
+      <c r="AF128" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="131" spans="31:31">
-      <c r="AE131" t="s">
+    <row r="129" spans="32:32">
+      <c r="AF129" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="132" spans="31:31">
-      <c r="AE132" t="s">
+    <row r="130" spans="32:32">
+      <c r="AF130" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="133" spans="31:31">
-      <c r="AE133" t="s">
+    <row r="131" spans="32:32">
+      <c r="AF131" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="134" spans="31:31">
-      <c r="AE134" t="s">
+    <row r="132" spans="32:32">
+      <c r="AF132" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="135" spans="31:31">
-      <c r="AE135" t="s">
+    <row r="133" spans="32:32">
+      <c r="AF133" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="136" spans="31:31">
-      <c r="AE136" t="s">
+    <row r="134" spans="32:32">
+      <c r="AF134" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="137" spans="31:31">
-      <c r="AE137" t="s">
+    <row r="135" spans="32:32">
+      <c r="AF135" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="138" spans="31:31">
-      <c r="AE138" t="s">
+    <row r="136" spans="32:32">
+      <c r="AF136" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="139" spans="31:31">
-      <c r="AE139" t="s">
+    <row r="137" spans="32:32">
+      <c r="AF137" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="140" spans="31:31">
-      <c r="AE140" t="s">
+    <row r="138" spans="32:32">
+      <c r="AF138" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="141" spans="31:31">
-      <c r="AE141" t="s">
+    <row r="139" spans="32:32">
+      <c r="AF139" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="142" spans="31:31">
-      <c r="AE142" t="s">
+    <row r="140" spans="32:32">
+      <c r="AF140" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="143" spans="31:31">
-      <c r="AE143" t="s">
+    <row r="141" spans="32:32">
+      <c r="AF141" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="144" spans="31:31">
-      <c r="AE144" t="s">
+    <row r="142" spans="32:32">
+      <c r="AF142" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="145" spans="31:31">
-      <c r="AE145" t="s">
+    <row r="143" spans="32:32">
+      <c r="AF143" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="146" spans="31:31">
-      <c r="AE146" t="s">
+    <row r="144" spans="32:32">
+      <c r="AF144" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="147" spans="31:31">
-      <c r="AE147" t="s">
+    <row r="145" spans="32:32">
+      <c r="AF145" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="148" spans="31:31">
-      <c r="AE148" t="s">
+    <row r="146" spans="32:32">
+      <c r="AF146" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="149" spans="31:31">
-      <c r="AE149" t="s">
+    <row r="147" spans="32:32">
+      <c r="AF147" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="150" spans="31:31">
-      <c r="AE150" t="s">
+    <row r="148" spans="32:32">
+      <c r="AF148" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="151" spans="31:31">
-      <c r="AE151" t="s">
+    <row r="149" spans="32:32">
+      <c r="AF149" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="152" spans="31:31">
-      <c r="AE152" t="s">
+    <row r="150" spans="32:32">
+      <c r="AF150" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="153" spans="31:31">
-      <c r="AE153" t="s">
+    <row r="151" spans="32:32">
+      <c r="AF151" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="154" spans="31:31">
-      <c r="AE154" t="s">
+    <row r="152" spans="32:32">
+      <c r="AF152" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="155" spans="31:31">
-      <c r="AE155" t="s">
+    <row r="153" spans="32:32">
+      <c r="AF153" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="156" spans="31:31">
-      <c r="AE156" t="s">
+    <row r="154" spans="32:32">
+      <c r="AF154" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="157" spans="31:31">
-      <c r="AE157" t="s">
+    <row r="155" spans="32:32">
+      <c r="AF155" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="158" spans="31:31">
-      <c r="AE158" t="s">
+    <row r="156" spans="32:32">
+      <c r="AF156" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="159" spans="31:31">
-      <c r="AE159" t="s">
+    <row r="157" spans="32:32">
+      <c r="AF157" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="160" spans="31:31">
-      <c r="AE160" t="s">
+    <row r="158" spans="32:32">
+      <c r="AF158" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="161" spans="31:31">
-      <c r="AE161" t="s">
+    <row r="159" spans="32:32">
+      <c r="AF159" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="162" spans="31:31">
-      <c r="AE162" t="s">
+    <row r="160" spans="32:32">
+      <c r="AF160" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="163" spans="31:31">
-      <c r="AE163" t="s">
+    <row r="161" spans="32:32">
+      <c r="AF161" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="164" spans="31:31">
-      <c r="AE164" t="s">
+    <row r="162" spans="32:32">
+      <c r="AF162" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="165" spans="31:31">
-      <c r="AE165" t="s">
+    <row r="163" spans="32:32">
+      <c r="AF163" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="166" spans="31:31">
-      <c r="AE166" t="s">
+    <row r="164" spans="32:32">
+      <c r="AF164" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="167" spans="31:31">
-      <c r="AE167" t="s">
+    <row r="165" spans="32:32">
+      <c r="AF165" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="168" spans="31:31">
-      <c r="AE168" t="s">
+    <row r="166" spans="32:32">
+      <c r="AF166" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="169" spans="31:31">
-      <c r="AE169" t="s">
+    <row r="167" spans="32:32">
+      <c r="AF167" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="170" spans="31:31">
-      <c r="AE170" t="s">
+    <row r="168" spans="32:32">
+      <c r="AF168" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="171" spans="31:31">
-      <c r="AE171" t="s">
+    <row r="169" spans="32:32">
+      <c r="AF169" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="172" spans="31:31">
-      <c r="AE172" t="s">
+    <row r="170" spans="32:32">
+      <c r="AF170" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="173" spans="31:31">
-      <c r="AE173" t="s">
+    <row r="171" spans="32:32">
+      <c r="AF171" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="174" spans="31:31">
-      <c r="AE174" t="s">
+    <row r="172" spans="32:32">
+      <c r="AF172" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="175" spans="31:31">
-      <c r="AE175" t="s">
+    <row r="173" spans="32:32">
+      <c r="AF173" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="176" spans="31:31">
-      <c r="AE176" t="s">
+    <row r="174" spans="32:32">
+      <c r="AF174" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="177" spans="31:31">
-      <c r="AE177" t="s">
+    <row r="175" spans="32:32">
+      <c r="AF175" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="178" spans="31:31">
-      <c r="AE178" t="s">
+    <row r="176" spans="32:32">
+      <c r="AF176" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="179" spans="31:31">
-      <c r="AE179" t="s">
+    <row r="177" spans="32:32">
+      <c r="AF177" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="180" spans="31:31">
-      <c r="AE180" t="s">
+    <row r="178" spans="32:32">
+      <c r="AF178" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="181" spans="31:31">
-      <c r="AE181" t="s">
+    <row r="179" spans="32:32">
+      <c r="AF179" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="182" spans="31:31">
-      <c r="AE182" t="s">
+    <row r="180" spans="32:32">
+      <c r="AF180" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="183" spans="31:31">
-      <c r="AE183" t="s">
+    <row r="181" spans="32:32">
+      <c r="AF181" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="184" spans="31:31">
-      <c r="AE184" t="s">
+    <row r="182" spans="32:32">
+      <c r="AF182" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="185" spans="31:31">
-      <c r="AE185" t="s">
+    <row r="183" spans="32:32">
+      <c r="AF183" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="186" spans="31:31">
-      <c r="AE186" t="s">
+    <row r="184" spans="32:32">
+      <c r="AF184" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="187" spans="31:31">
-      <c r="AE187" t="s">
+    <row r="185" spans="32:32">
+      <c r="AF185" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="188" spans="31:31">
-      <c r="AE188" t="s">
+    <row r="186" spans="32:32">
+      <c r="AF186" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="189" spans="31:31">
-      <c r="AE189" t="s">
+    <row r="187" spans="32:32">
+      <c r="AF187" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="190" spans="31:31">
-      <c r="AE190" t="s">
+    <row r="188" spans="32:32">
+      <c r="AF188" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="191" spans="31:31">
-      <c r="AE191" t="s">
+    <row r="189" spans="32:32">
+      <c r="AF189" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="192" spans="31:31">
-      <c r="AE192" t="s">
+    <row r="190" spans="32:32">
+      <c r="AF190" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="193" spans="31:31">
-      <c r="AE193" t="s">
+    <row r="191" spans="32:32">
+      <c r="AF191" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="194" spans="31:31">
-      <c r="AE194" t="s">
+    <row r="192" spans="32:32">
+      <c r="AF192" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="195" spans="31:31">
-      <c r="AE195" t="s">
+    <row r="193" spans="32:32">
+      <c r="AF193" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="196" spans="31:31">
-      <c r="AE196" t="s">
+    <row r="194" spans="32:32">
+      <c r="AF194" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="197" spans="31:31">
-      <c r="AE197" t="s">
+    <row r="195" spans="32:32">
+      <c r="AF195" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="198" spans="31:31">
-      <c r="AE198" t="s">
+    <row r="196" spans="32:32">
+      <c r="AF196" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="199" spans="31:31">
-      <c r="AE199" t="s">
+    <row r="197" spans="32:32">
+      <c r="AF197" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="200" spans="31:31">
-      <c r="AE200" t="s">
+    <row r="198" spans="32:32">
+      <c r="AF198" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="201" spans="31:31">
-      <c r="AE201" t="s">
+    <row r="199" spans="32:32">
+      <c r="AF199" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="202" spans="31:31">
-      <c r="AE202" t="s">
+    <row r="200" spans="32:32">
+      <c r="AF200" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="203" spans="31:31">
-      <c r="AE203" t="s">
+    <row r="201" spans="32:32">
+      <c r="AF201" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="204" spans="31:31">
-      <c r="AE204" t="s">
+    <row r="202" spans="32:32">
+      <c r="AF202" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="205" spans="31:31">
-      <c r="AE205" t="s">
+    <row r="203" spans="32:32">
+      <c r="AF203" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="206" spans="31:31">
-      <c r="AE206" t="s">
+    <row r="204" spans="32:32">
+      <c r="AF204" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="207" spans="31:31">
-      <c r="AE207" t="s">
+    <row r="205" spans="32:32">
+      <c r="AF205" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="208" spans="31:31">
-      <c r="AE208" t="s">
+    <row r="206" spans="32:32">
+      <c r="AF206" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="209" spans="31:31">
-      <c r="AE209" t="s">
+    <row r="207" spans="32:32">
+      <c r="AF207" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="210" spans="31:31">
-      <c r="AE210" t="s">
+    <row r="208" spans="32:32">
+      <c r="AF208" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="211" spans="31:31">
-      <c r="AE211" t="s">
+    <row r="209" spans="32:32">
+      <c r="AF209" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="212" spans="31:31">
-      <c r="AE212" t="s">
+    <row r="210" spans="32:32">
+      <c r="AF210" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="213" spans="31:31">
-      <c r="AE213" t="s">
+    <row r="211" spans="32:32">
+      <c r="AF211" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="214" spans="31:31">
-      <c r="AE214" t="s">
+    <row r="212" spans="32:32">
+      <c r="AF212" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="215" spans="31:31">
-      <c r="AE215" t="s">
+    <row r="213" spans="32:32">
+      <c r="AF213" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="216" spans="31:31">
-      <c r="AE216" t="s">
+    <row r="214" spans="32:32">
+      <c r="AF214" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="217" spans="31:31">
-      <c r="AE217" t="s">
+    <row r="215" spans="32:32">
+      <c r="AF215" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="218" spans="31:31">
-      <c r="AE218" t="s">
+    <row r="216" spans="32:32">
+      <c r="AF216" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="219" spans="31:31">
-      <c r="AE219" t="s">
+    <row r="217" spans="32:32">
+      <c r="AF217" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="220" spans="31:31">
-      <c r="AE220" t="s">
+    <row r="218" spans="32:32">
+      <c r="AF218" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="221" spans="31:31">
-      <c r="AE221" t="s">
+    <row r="219" spans="32:32">
+      <c r="AF219" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="222" spans="31:31">
-      <c r="AE222" t="s">
+    <row r="220" spans="32:32">
+      <c r="AF220" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="223" spans="31:31">
-      <c r="AE223" t="s">
+    <row r="221" spans="32:32">
+      <c r="AF221" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="224" spans="31:31">
-      <c r="AE224" t="s">
+    <row r="222" spans="32:32">
+      <c r="AF222" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="225" spans="31:31">
-      <c r="AE225" t="s">
+    <row r="223" spans="32:32">
+      <c r="AF223" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="226" spans="31:31">
-      <c r="AE226" t="s">
+    <row r="224" spans="32:32">
+      <c r="AF224" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="227" spans="31:31">
-      <c r="AE227" t="s">
+    <row r="225" spans="32:32">
+      <c r="AF225" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="228" spans="31:31">
-      <c r="AE228" t="s">
+    <row r="226" spans="32:32">
+      <c r="AF226" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="229" spans="31:31">
-      <c r="AE229" t="s">
+    <row r="227" spans="32:32">
+      <c r="AF227" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="230" spans="31:31">
-      <c r="AE230" t="s">
+    <row r="228" spans="32:32">
+      <c r="AF228" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="231" spans="31:31">
-      <c r="AE231" t="s">
+    <row r="229" spans="32:32">
+      <c r="AF229" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="232" spans="31:31">
-      <c r="AE232" t="s">
+    <row r="230" spans="32:32">
+      <c r="AF230" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="233" spans="31:31">
-      <c r="AE233" t="s">
+    <row r="231" spans="32:32">
+      <c r="AF231" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="234" spans="31:31">
-      <c r="AE234" t="s">
+    <row r="232" spans="32:32">
+      <c r="AF232" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="235" spans="31:31">
-      <c r="AE235" t="s">
+    <row r="233" spans="32:32">
+      <c r="AF233" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="236" spans="31:31">
-      <c r="AE236" t="s">
+    <row r="234" spans="32:32">
+      <c r="AF234" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="237" spans="31:31">
-      <c r="AE237" t="s">
+    <row r="235" spans="32:32">
+      <c r="AF235" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="238" spans="31:31">
-      <c r="AE238" t="s">
+    <row r="236" spans="32:32">
+      <c r="AF236" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="239" spans="31:31">
-      <c r="AE239" t="s">
+    <row r="237" spans="32:32">
+      <c r="AF237" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="240" spans="31:31">
-      <c r="AE240" t="s">
+    <row r="238" spans="32:32">
+      <c r="AF238" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="241" spans="31:31">
-      <c r="AE241" t="s">
+    <row r="239" spans="32:32">
+      <c r="AF239" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="242" spans="31:31">
-      <c r="AE242" t="s">
+    <row r="240" spans="32:32">
+      <c r="AF240" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="243" spans="31:31">
-      <c r="AE243" t="s">
+    <row r="241" spans="32:32">
+      <c r="AF241" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="244" spans="31:31">
-      <c r="AE244" t="s">
+    <row r="242" spans="32:32">
+      <c r="AF242" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="245" spans="31:31">
-      <c r="AE245" t="s">
+    <row r="243" spans="32:32">
+      <c r="AF243" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="246" spans="31:31">
-      <c r="AE246" t="s">
+    <row r="244" spans="32:32">
+      <c r="AF244" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="247" spans="31:31">
-      <c r="AE247" t="s">
+    <row r="245" spans="32:32">
+      <c r="AF245" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="248" spans="31:31">
-      <c r="AE248" t="s">
+    <row r="246" spans="32:32">
+      <c r="AF246" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="249" spans="31:31">
-      <c r="AE249" t="s">
+    <row r="247" spans="32:32">
+      <c r="AF247" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="250" spans="31:31">
-      <c r="AE250" t="s">
+    <row r="248" spans="32:32">
+      <c r="AF248" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="251" spans="31:31">
-      <c r="AE251" t="s">
+    <row r="249" spans="32:32">
+      <c r="AF249" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="252" spans="31:31">
-      <c r="AE252" t="s">
+    <row r="250" spans="32:32">
+      <c r="AF250" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="253" spans="31:31">
-      <c r="AE253" t="s">
+    <row r="251" spans="32:32">
+      <c r="AF251" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="254" spans="31:31">
-      <c r="AE254" t="s">
+    <row r="252" spans="32:32">
+      <c r="AF252" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="255" spans="31:31">
-      <c r="AE255" t="s">
+    <row r="253" spans="32:32">
+      <c r="AF253" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="256" spans="31:31">
-      <c r="AE256" t="s">
+    <row r="254" spans="32:32">
+      <c r="AF254" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="257" spans="31:31">
-      <c r="AE257" t="s">
+    <row r="255" spans="32:32">
+      <c r="AF255" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="258" spans="31:31">
-      <c r="AE258" t="s">
+    <row r="256" spans="32:32">
+      <c r="AF256" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="259" spans="31:31">
-      <c r="AE259" t="s">
+    <row r="257" spans="32:32">
+      <c r="AF257" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="260" spans="31:31">
-      <c r="AE260" t="s">
+    <row r="258" spans="32:32">
+      <c r="AF258" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="261" spans="31:31">
-      <c r="AE261" t="s">
+    <row r="259" spans="32:32">
+      <c r="AF259" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="262" spans="31:31">
-      <c r="AE262" t="s">
+    <row r="260" spans="32:32">
+      <c r="AF260" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="263" spans="31:31">
-      <c r="AE263" t="s">
+    <row r="261" spans="32:32">
+      <c r="AF261" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="264" spans="31:31">
-      <c r="AE264" t="s">
+    <row r="262" spans="32:32">
+      <c r="AF262" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="265" spans="31:31">
-      <c r="AE265" t="s">
+    <row r="263" spans="32:32">
+      <c r="AF263" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="266" spans="31:31">
-      <c r="AE266" t="s">
+    <row r="264" spans="32:32">
+      <c r="AF264" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="267" spans="31:31">
-      <c r="AE267" t="s">
+    <row r="265" spans="32:32">
+      <c r="AF265" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="268" spans="31:31">
-      <c r="AE268" t="s">
+    <row r="266" spans="32:32">
+      <c r="AF266" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="269" spans="31:31">
-      <c r="AE269" t="s">
+    <row r="267" spans="32:32">
+      <c r="AF267" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="270" spans="31:31">
-      <c r="AE270" t="s">
+    <row r="268" spans="32:32">
+      <c r="AF268" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="271" spans="31:31">
-      <c r="AE271" t="s">
+    <row r="269" spans="32:32">
+      <c r="AF269" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="272" spans="31:31">
-      <c r="AE272" t="s">
+    <row r="270" spans="32:32">
+      <c r="AF270" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="273" spans="31:31">
-      <c r="AE273" t="s">
+    <row r="271" spans="32:32">
+      <c r="AF271" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="274" spans="31:31">
-      <c r="AE274" t="s">
+    <row r="272" spans="32:32">
+      <c r="AF272" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="275" spans="31:31">
-      <c r="AE275" t="s">
+    <row r="273" spans="32:32">
+      <c r="AF273" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="276" spans="31:31">
-      <c r="AE276" t="s">
+    <row r="274" spans="32:32">
+      <c r="AF274" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="277" spans="31:31">
-      <c r="AE277" t="s">
+    <row r="275" spans="32:32">
+      <c r="AF275" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="278" spans="31:31">
-      <c r="AE278" t="s">
+    <row r="276" spans="32:32">
+      <c r="AF276" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="279" spans="31:31">
-      <c r="AE279" t="s">
+    <row r="277" spans="32:32">
+      <c r="AF277" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="280" spans="31:31">
-      <c r="AE280" t="s">
+    <row r="278" spans="32:32">
+      <c r="AF278" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="281" spans="31:31">
-      <c r="AE281" t="s">
+    <row r="279" spans="32:32">
+      <c r="AF279" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="282" spans="31:31">
-      <c r="AE282" t="s">
+    <row r="280" spans="32:32">
+      <c r="AF280" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="283" spans="31:31">
-      <c r="AE283" t="s">
+    <row r="281" spans="32:32">
+      <c r="AF281" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="284" spans="31:31">
-      <c r="AE284" t="s">
+    <row r="282" spans="32:32">
+      <c r="AF282" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="285" spans="31:31">
-      <c r="AE285" t="s">
+    <row r="283" spans="32:32">
+      <c r="AF283" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="286" spans="31:31">
-      <c r="AE286" t="s">
+    <row r="284" spans="32:32">
+      <c r="AF284" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="287" spans="31:31">
-      <c r="AE287" t="s">
+    <row r="285" spans="32:32">
+      <c r="AF285" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="288" spans="31:31">
-      <c r="AE288" t="s">
+    <row r="286" spans="32:32">
+      <c r="AF286" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="289" spans="31:31">
-      <c r="AE289" t="s">
+    <row r="287" spans="32:32">
+      <c r="AF287" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="290" spans="31:31">
-      <c r="AE290" t="s">
+    <row r="288" spans="32:32">
+      <c r="AF288" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="291" spans="31:31">
-      <c r="AE291" t="s">
+    <row r="289" spans="32:32">
+      <c r="AF289" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="292" spans="31:31">
-      <c r="AE292" t="s">
+    <row r="290" spans="32:32">
+      <c r="AF290" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="293" spans="31:31">
-      <c r="AE293" t="s">
+    <row r="291" spans="32:32">
+      <c r="AF291" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="294" spans="31:31">
-      <c r="AE294" t="s">
+    <row r="292" spans="32:32">
+      <c r="AF292" t="s">
         <v>622</v>
+      </c>
+    </row>
+    <row r="293" spans="32:32">
+      <c r="AF293" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="294" spans="32:32">
+      <c r="AF294" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000038/metadata_template_ERC000038.xlsx
+++ b/templates/ERC000038/metadata_template_ERC000038.xlsx
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="aquacultureorigin">'cv_sample'!$K$1:$K$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AF$1:$AF$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AF$1:$AF$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
-    <definedName name="platform">'cv_experiment'!$M$1:$M$17</definedName>
+    <definedName name="platform">'cv_experiment'!$M$1:$M$18</definedName>
     <definedName name="samplehealthstate">'cv_sample'!$Q$1:$Q$2</definedName>
     <definedName name="studytype">'cv_study'!$C$1:$C$15</definedName>
   </definedNames>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="633">
   <si>
     <t>alias</t>
   </si>
@@ -449,6 +449,9 @@
     <t>ELEMENT</t>
   </si>
   <si>
+    <t>AVITI</t>
+  </si>
+  <si>
     <t>ULTIMA</t>
   </si>
   <si>
@@ -539,6 +542,9 @@
     <t>AB SOLiD System 3.0</t>
   </si>
   <si>
+    <t>AVITI 24</t>
+  </si>
+  <si>
     <t>BGISEQ-50</t>
   </si>
   <si>
@@ -1235,9 +1241,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1256,6 +1259,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1457,6 +1463,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1466,9 +1475,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1508,7 +1514,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1577,6 +1583,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1652,6 +1661,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1673,6 +1685,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1718,6 +1733,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1730,6 +1748,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1739,9 +1760,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1766,6 +1784,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1826,10 +1847,10 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
   </si>
   <si>
     <t>Wallis and Futuna</t>
@@ -2437,10 +2458,10 @@
         <v>124</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2481,10 +2502,10 @@
         <v>125</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2532,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N87"/>
+  <dimension ref="G1:N88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -2528,7 +2549,7 @@
         <v>126</v>
       </c>
       <c r="N1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="7:14">
@@ -2545,7 +2566,7 @@
         <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="7:14">
@@ -2562,7 +2583,7 @@
         <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="7:14">
@@ -2579,7 +2600,7 @@
         <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="7:14">
@@ -2596,7 +2617,7 @@
         <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="7:14">
@@ -2613,7 +2634,7 @@
         <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="7:14">
@@ -2630,7 +2651,7 @@
         <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="7:14">
@@ -2647,7 +2668,7 @@
         <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="7:14">
@@ -2664,7 +2685,7 @@
         <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="7:14">
@@ -2678,7 +2699,7 @@
         <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="7:14">
@@ -2692,7 +2713,7 @@
         <v>136</v>
       </c>
       <c r="N11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="7:14">
@@ -2706,7 +2727,7 @@
         <v>137</v>
       </c>
       <c r="N12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="7:14">
@@ -2720,7 +2741,7 @@
         <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="7:14">
@@ -2734,7 +2755,7 @@
         <v>139</v>
       </c>
       <c r="N14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="7:14">
@@ -2748,7 +2769,7 @@
         <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="7:14">
@@ -2762,7 +2783,7 @@
         <v>141</v>
       </c>
       <c r="N16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="7:14">
@@ -2776,7 +2797,7 @@
         <v>142</v>
       </c>
       <c r="N17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="7:14">
@@ -2786,8 +2807,11 @@
       <c r="I18" t="s">
         <v>54</v>
       </c>
+      <c r="M18" t="s">
+        <v>143</v>
+      </c>
       <c r="N18" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="7:14">
@@ -2798,7 +2822,7 @@
         <v>105</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="7:14">
@@ -2809,7 +2833,7 @@
         <v>106</v>
       </c>
       <c r="N20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="7:14">
@@ -2820,7 +2844,7 @@
         <v>107</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="7:14">
@@ -2831,7 +2855,7 @@
         <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="7:14">
@@ -2842,7 +2866,7 @@
         <v>109</v>
       </c>
       <c r="N23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="7:14">
@@ -2853,7 +2877,7 @@
         <v>110</v>
       </c>
       <c r="N24" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="7:14">
@@ -2864,7 +2888,7 @@
         <v>111</v>
       </c>
       <c r="N25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="7:14">
@@ -2875,7 +2899,7 @@
         <v>112</v>
       </c>
       <c r="N26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="7:14">
@@ -2886,7 +2910,7 @@
         <v>113</v>
       </c>
       <c r="N27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="7:14">
@@ -2897,7 +2921,7 @@
         <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="7:14">
@@ -2908,7 +2932,7 @@
         <v>115</v>
       </c>
       <c r="N29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="7:14">
@@ -2919,7 +2943,7 @@
         <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="7:14">
@@ -2930,7 +2954,7 @@
         <v>117</v>
       </c>
       <c r="N31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="7:14">
@@ -2938,7 +2962,7 @@
         <v>66</v>
       </c>
       <c r="N32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="7:14">
@@ -2946,7 +2970,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="7:14">
@@ -2954,7 +2978,7 @@
         <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="7:14">
@@ -2962,7 +2986,7 @@
         <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="7:14">
@@ -2970,7 +2994,7 @@
         <v>70</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="7:14">
@@ -2978,7 +3002,7 @@
         <v>71</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="7:14">
@@ -2986,7 +3010,7 @@
         <v>72</v>
       </c>
       <c r="N38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="7:14">
@@ -2994,7 +3018,7 @@
         <v>73</v>
       </c>
       <c r="N39" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="7:14">
@@ -3002,7 +3026,7 @@
         <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="7:14">
@@ -3010,236 +3034,241 @@
         <v>75</v>
       </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="7:14">
       <c r="N42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43" spans="7:14">
       <c r="N43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" spans="7:14">
       <c r="N44" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="7:14">
       <c r="N45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="46" spans="7:14">
       <c r="N46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="7:14">
       <c r="N47" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="7:14">
       <c r="N48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49" spans="14:14">
       <c r="N49" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" spans="14:14">
       <c r="N50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="14:14">
       <c r="N51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="14:14">
       <c r="N52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="53" spans="14:14">
       <c r="N53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="14:14">
       <c r="N54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="14:14">
       <c r="N55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="14:14">
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="14:14">
       <c r="N57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="14:14">
       <c r="N58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="14:14">
       <c r="N59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="14:14">
       <c r="N60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="14:14">
       <c r="N61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="14:14">
       <c r="N62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="14:14">
       <c r="N63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="14:14">
       <c r="N64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" spans="14:14">
       <c r="N65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="14:14">
       <c r="N66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="67" spans="14:14">
       <c r="N67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="14:14">
       <c r="N68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="14:14">
       <c r="N69" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="14:14">
       <c r="N70" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="14:14">
       <c r="N71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="72" spans="14:14">
       <c r="N72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="14:14">
       <c r="N73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74" spans="14:14">
       <c r="N74" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="14:14">
       <c r="N75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="14:14">
       <c r="N76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" spans="14:14">
       <c r="N77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="14:14">
       <c r="N78" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="14:14">
       <c r="N79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80" spans="14:14">
       <c r="N80" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="14:14">
       <c r="N81" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="14:14">
       <c r="N82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="14:14">
       <c r="N83" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="14:14">
       <c r="N84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="14:14">
       <c r="N87" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14">
+      <c r="N88" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3261,27 +3290,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -3301,122 +3330,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3440,210 +3469,210 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -3664,1467 +3693,1492 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="K1:AF289"/>
+  <dimension ref="K1:AF294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="11:32">
       <c r="K1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AF1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="11:32">
       <c r="K2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AF2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="11:32">
       <c r="K3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AF3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="11:32">
       <c r="AF4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="11:32">
       <c r="AF5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6" spans="11:32">
       <c r="AF6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="11:32">
       <c r="AF7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="11:32">
       <c r="AF8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="11:32">
       <c r="AF9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="11:32">
       <c r="AF10" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="11:32">
       <c r="AF11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="11:32">
       <c r="AF12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="11:32">
       <c r="AF13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="11:32">
       <c r="AF14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="11:32">
       <c r="AF15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="11:32">
       <c r="AF16" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="32:32">
       <c r="AF17" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="32:32">
       <c r="AF18" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="32:32">
       <c r="AF19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="32:32">
       <c r="AF20" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="32:32">
       <c r="AF21" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="32:32">
       <c r="AF22" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="32:32">
       <c r="AF23" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="32:32">
       <c r="AF24" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="32:32">
       <c r="AF25" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="32:32">
       <c r="AF26" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="32:32">
       <c r="AF27" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="32:32">
       <c r="AF28" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="32:32">
       <c r="AF29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30" spans="32:32">
       <c r="AF30" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="32:32">
       <c r="AF31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="32:32">
       <c r="AF32" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33" spans="32:32">
       <c r="AF33" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="34" spans="32:32">
       <c r="AF34" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" spans="32:32">
       <c r="AF35" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" spans="32:32">
       <c r="AF36" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="32:32">
       <c r="AF37" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="32:32">
       <c r="AF38" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="32:32">
       <c r="AF39" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="32:32">
       <c r="AF40" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="32:32">
       <c r="AF41" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="42" spans="32:32">
       <c r="AF42" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43" spans="32:32">
       <c r="AF43" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="32:32">
       <c r="AF44" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="32:32">
       <c r="AF45" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="32:32">
       <c r="AF46" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="32:32">
       <c r="AF47" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="32:32">
       <c r="AF48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="32:32">
       <c r="AF49" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="32:32">
       <c r="AF50" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="32:32">
       <c r="AF51" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="32:32">
       <c r="AF52" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="32:32">
       <c r="AF53" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="32:32">
       <c r="AF54" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="32:32">
       <c r="AF55" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="32:32">
       <c r="AF56" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="32:32">
       <c r="AF57" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="32:32">
       <c r="AF58" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="32:32">
       <c r="AF59" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="32:32">
       <c r="AF60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="32:32">
       <c r="AF61" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="32:32">
       <c r="AF62" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="32:32">
       <c r="AF63" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64" spans="32:32">
       <c r="AF64" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="32:32">
       <c r="AF65" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="32:32">
       <c r="AF66" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="32:32">
       <c r="AF67" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="32:32">
       <c r="AF68" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="32:32">
       <c r="AF69" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="32:32">
       <c r="AF70" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="32:32">
       <c r="AF71" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="32:32">
       <c r="AF72" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="32:32">
       <c r="AF73" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="74" spans="32:32">
       <c r="AF74" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="32:32">
       <c r="AF75" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="76" spans="32:32">
       <c r="AF76" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="77" spans="32:32">
       <c r="AF77" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="32:32">
       <c r="AF78" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="79" spans="32:32">
       <c r="AF79" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="32:32">
       <c r="AF80" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="81" spans="32:32">
       <c r="AF81" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="82" spans="32:32">
       <c r="AF82" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="83" spans="32:32">
       <c r="AF83" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="84" spans="32:32">
       <c r="AF84" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="85" spans="32:32">
       <c r="AF85" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="32:32">
       <c r="AF86" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="87" spans="32:32">
       <c r="AF87" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="88" spans="32:32">
       <c r="AF88" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="32:32">
       <c r="AF89" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="90" spans="32:32">
       <c r="AF90" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="91" spans="32:32">
       <c r="AF91" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="92" spans="32:32">
       <c r="AF92" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="93" spans="32:32">
       <c r="AF93" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="94" spans="32:32">
       <c r="AF94" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="95" spans="32:32">
       <c r="AF95" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="96" spans="32:32">
       <c r="AF96" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="32:32">
       <c r="AF97" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="32:32">
       <c r="AF98" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="32:32">
       <c r="AF99" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="100" spans="32:32">
       <c r="AF100" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="32:32">
       <c r="AF101" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="102" spans="32:32">
       <c r="AF102" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="32:32">
       <c r="AF103" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="32:32">
       <c r="AF104" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="32:32">
       <c r="AF105" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="32:32">
       <c r="AF106" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="32:32">
       <c r="AF107" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="32:32">
       <c r="AF108" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="109" spans="32:32">
       <c r="AF109" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="110" spans="32:32">
       <c r="AF110" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="32:32">
       <c r="AF111" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="32:32">
       <c r="AF112" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="113" spans="32:32">
       <c r="AF113" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="114" spans="32:32">
       <c r="AF114" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="32:32">
       <c r="AF115" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="116" spans="32:32">
       <c r="AF116" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="117" spans="32:32">
       <c r="AF117" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="32:32">
       <c r="AF118" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="119" spans="32:32">
       <c r="AF119" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="120" spans="32:32">
       <c r="AF120" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="121" spans="32:32">
       <c r="AF121" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="122" spans="32:32">
       <c r="AF122" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="32:32">
       <c r="AF123" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="124" spans="32:32">
       <c r="AF124" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="125" spans="32:32">
       <c r="AF125" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="126" spans="32:32">
       <c r="AF126" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="127" spans="32:32">
       <c r="AF127" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="128" spans="32:32">
       <c r="AF128" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="129" spans="32:32">
       <c r="AF129" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="130" spans="32:32">
       <c r="AF130" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="131" spans="32:32">
       <c r="AF131" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="132" spans="32:32">
       <c r="AF132" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="133" spans="32:32">
       <c r="AF133" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="134" spans="32:32">
       <c r="AF134" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="135" spans="32:32">
       <c r="AF135" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="136" spans="32:32">
       <c r="AF136" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="137" spans="32:32">
       <c r="AF137" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="138" spans="32:32">
       <c r="AF138" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="139" spans="32:32">
       <c r="AF139" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="32:32">
       <c r="AF140" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="141" spans="32:32">
       <c r="AF141" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="142" spans="32:32">
       <c r="AF142" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="143" spans="32:32">
       <c r="AF143" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="144" spans="32:32">
       <c r="AF144" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="145" spans="32:32">
       <c r="AF145" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="146" spans="32:32">
       <c r="AF146" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="147" spans="32:32">
       <c r="AF147" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="148" spans="32:32">
       <c r="AF148" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="149" spans="32:32">
       <c r="AF149" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="150" spans="32:32">
       <c r="AF150" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="151" spans="32:32">
       <c r="AF151" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="152" spans="32:32">
       <c r="AF152" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="153" spans="32:32">
       <c r="AF153" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="154" spans="32:32">
       <c r="AF154" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="155" spans="32:32">
       <c r="AF155" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="156" spans="32:32">
       <c r="AF156" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157" spans="32:32">
       <c r="AF157" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="158" spans="32:32">
       <c r="AF158" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="159" spans="32:32">
       <c r="AF159" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="160" spans="32:32">
       <c r="AF160" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="161" spans="32:32">
       <c r="AF161" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="162" spans="32:32">
       <c r="AF162" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="163" spans="32:32">
       <c r="AF163" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="164" spans="32:32">
       <c r="AF164" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="165" spans="32:32">
       <c r="AF165" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="166" spans="32:32">
       <c r="AF166" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="167" spans="32:32">
       <c r="AF167" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="168" spans="32:32">
       <c r="AF168" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="169" spans="32:32">
       <c r="AF169" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="170" spans="32:32">
       <c r="AF170" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="171" spans="32:32">
       <c r="AF171" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="172" spans="32:32">
       <c r="AF172" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="173" spans="32:32">
       <c r="AF173" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="174" spans="32:32">
       <c r="AF174" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="175" spans="32:32">
       <c r="AF175" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="176" spans="32:32">
       <c r="AF176" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="177" spans="32:32">
       <c r="AF177" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="178" spans="32:32">
       <c r="AF178" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="179" spans="32:32">
       <c r="AF179" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="180" spans="32:32">
       <c r="AF180" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="181" spans="32:32">
       <c r="AF181" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="182" spans="32:32">
       <c r="AF182" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="183" spans="32:32">
       <c r="AF183" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="184" spans="32:32">
       <c r="AF184" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="185" spans="32:32">
       <c r="AF185" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="186" spans="32:32">
       <c r="AF186" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="187" spans="32:32">
       <c r="AF187" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="188" spans="32:32">
       <c r="AF188" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="189" spans="32:32">
       <c r="AF189" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="190" spans="32:32">
       <c r="AF190" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="191" spans="32:32">
       <c r="AF191" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="192" spans="32:32">
       <c r="AF192" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="193" spans="32:32">
       <c r="AF193" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="194" spans="32:32">
       <c r="AF194" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="195" spans="32:32">
       <c r="AF195" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="196" spans="32:32">
       <c r="AF196" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="197" spans="32:32">
       <c r="AF197" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="32:32">
       <c r="AF198" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="199" spans="32:32">
       <c r="AF199" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="200" spans="32:32">
       <c r="AF200" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="201" spans="32:32">
       <c r="AF201" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="202" spans="32:32">
       <c r="AF202" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="203" spans="32:32">
       <c r="AF203" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="204" spans="32:32">
       <c r="AF204" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="205" spans="32:32">
       <c r="AF205" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="206" spans="32:32">
       <c r="AF206" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="207" spans="32:32">
       <c r="AF207" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="208" spans="32:32">
       <c r="AF208" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="209" spans="32:32">
       <c r="AF209" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="210" spans="32:32">
       <c r="AF210" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="211" spans="32:32">
       <c r="AF211" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="212" spans="32:32">
       <c r="AF212" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="213" spans="32:32">
       <c r="AF213" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="214" spans="32:32">
       <c r="AF214" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="215" spans="32:32">
       <c r="AF215" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="216" spans="32:32">
       <c r="AF216" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="217" spans="32:32">
       <c r="AF217" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="218" spans="32:32">
       <c r="AF218" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="219" spans="32:32">
       <c r="AF219" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="220" spans="32:32">
       <c r="AF220" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="221" spans="32:32">
       <c r="AF221" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="222" spans="32:32">
       <c r="AF222" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="223" spans="32:32">
       <c r="AF223" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="224" spans="32:32">
       <c r="AF224" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="225" spans="32:32">
       <c r="AF225" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="226" spans="32:32">
       <c r="AF226" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="227" spans="32:32">
       <c r="AF227" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="228" spans="32:32">
       <c r="AF228" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="229" spans="32:32">
       <c r="AF229" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="230" spans="32:32">
       <c r="AF230" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="231" spans="32:32">
       <c r="AF231" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="232" spans="32:32">
       <c r="AF232" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="233" spans="32:32">
       <c r="AF233" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="234" spans="32:32">
       <c r="AF234" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="235" spans="32:32">
       <c r="AF235" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="236" spans="32:32">
       <c r="AF236" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="237" spans="32:32">
       <c r="AF237" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="238" spans="32:32">
       <c r="AF238" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="239" spans="32:32">
       <c r="AF239" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="240" spans="32:32">
       <c r="AF240" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="241" spans="32:32">
       <c r="AF241" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="242" spans="32:32">
       <c r="AF242" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="243" spans="32:32">
       <c r="AF243" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="244" spans="32:32">
       <c r="AF244" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="245" spans="32:32">
       <c r="AF245" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="246" spans="32:32">
       <c r="AF246" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="247" spans="32:32">
       <c r="AF247" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="248" spans="32:32">
       <c r="AF248" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="249" spans="32:32">
       <c r="AF249" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="250" spans="32:32">
       <c r="AF250" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="251" spans="32:32">
       <c r="AF251" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="252" spans="32:32">
       <c r="AF252" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="253" spans="32:32">
       <c r="AF253" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="254" spans="32:32">
       <c r="AF254" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="255" spans="32:32">
       <c r="AF255" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="256" spans="32:32">
       <c r="AF256" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="257" spans="32:32">
       <c r="AF257" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="258" spans="32:32">
       <c r="AF258" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="259" spans="32:32">
       <c r="AF259" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" spans="32:32">
       <c r="AF260" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="261" spans="32:32">
       <c r="AF261" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="262" spans="32:32">
       <c r="AF262" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="263" spans="32:32">
       <c r="AF263" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="264" spans="32:32">
       <c r="AF264" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="265" spans="32:32">
       <c r="AF265" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="266" spans="32:32">
       <c r="AF266" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="267" spans="32:32">
       <c r="AF267" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="268" spans="32:32">
       <c r="AF268" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="269" spans="32:32">
       <c r="AF269" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="270" spans="32:32">
       <c r="AF270" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="271" spans="32:32">
       <c r="AF271" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="272" spans="32:32">
       <c r="AF272" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="273" spans="32:32">
       <c r="AF273" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="274" spans="32:32">
       <c r="AF274" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="275" spans="32:32">
       <c r="AF275" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="276" spans="32:32">
       <c r="AF276" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="277" spans="32:32">
       <c r="AF277" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="278" spans="32:32">
       <c r="AF278" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="279" spans="32:32">
       <c r="AF279" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="280" spans="32:32">
       <c r="AF280" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="281" spans="32:32">
       <c r="AF281" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="282" spans="32:32">
       <c r="AF282" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="283" spans="32:32">
       <c r="AF283" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="284" spans="32:32">
       <c r="AF284" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="285" spans="32:32">
       <c r="AF285" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="286" spans="32:32">
       <c r="AF286" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="287" spans="32:32">
       <c r="AF287" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="288" spans="32:32">
       <c r="AF288" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="289" spans="32:32">
       <c r="AF289" t="s">
-        <v>617</v>
+        <v>619</v>
+      </c>
+    </row>
+    <row r="290" spans="32:32">
+      <c r="AF290" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="291" spans="32:32">
+      <c r="AF291" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="292" spans="32:32">
+      <c r="AF292" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="293" spans="32:32">
+      <c r="AF293" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="294" spans="32:32">
+      <c r="AF294" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000038/metadata_template_ERC000038.xlsx
+++ b/templates/ERC000038/metadata_template_ERC000038.xlsx
@@ -917,19 +917,19 @@
     <t>shell length</t>
   </si>
   <si>
-    <t>(Mandatory) Length of shell (perpendicular to the hinge) (Units: g)</t>
+    <t>(Mandatory) Length of shell (perpendicular to the hinge)</t>
   </si>
   <si>
     <t>shell width</t>
   </si>
   <si>
-    <t>(Mandatory) Width of shell (perpendicular angle to length) (Units: g)</t>
+    <t>(Mandatory) Width of shell (perpendicular angle to length)</t>
   </si>
   <si>
     <t>shell markings</t>
   </si>
   <si>
-    <t>(Recommended) Visible markings on outer shell (Units: g)</t>
+    <t>(Recommended) Visible markings on outer shell</t>
   </si>
   <si>
     <t>diseased</t>
@@ -1025,7 +1025,7 @@
     <t>toxin burden</t>
   </si>
   <si>
-    <t>(Recommended) Concentration of toxins in the organism at the time of sampling (Units: mg)</t>
+    <t>(Recommended) Concentration of toxins in the organism at the time of sampling</t>
   </si>
   <si>
     <t>Afghanistan</t>

--- a/templates/ERC000038/metadata_template_ERC000038.xlsx
+++ b/templates/ERC000038/metadata_template_ERC000038.xlsx
@@ -20,7 +20,7 @@
     <definedName name="aquacultureorigin">'cv_sample'!$K$1:$K$3</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AF$1:$AF$294</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$88</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$89</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="634">
   <si>
     <t>alias</t>
   </si>
@@ -729,6 +729,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>UG 200</t>
   </si>
   <si>
     <t>Vega</t>
@@ -2461,7 +2464,7 @@
         <v>144</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2505,7 +2508,7 @@
         <v>145</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -2532,7 +2535,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N88"/>
+  <dimension ref="G1:N89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3269,6 +3272,11 @@
     </row>
     <row r="88" spans="14:14">
       <c r="N88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14">
+      <c r="N89" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3290,27 +3298,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -3330,122 +3338,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3469,210 +3477,210 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" spans="1:35" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -3698,1487 +3706,1487 @@
   <sheetData>
     <row r="1" spans="11:32">
       <c r="K1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AF1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="11:32">
       <c r="K2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AF2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="11:32">
       <c r="K3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AF3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="11:32">
       <c r="AF4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="11:32">
       <c r="AF5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="11:32">
       <c r="AF6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="11:32">
       <c r="AF7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="11:32">
       <c r="AF8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="11:32">
       <c r="AF9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="11:32">
       <c r="AF10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="11:32">
       <c r="AF11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="11:32">
       <c r="AF12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="11:32">
       <c r="AF13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="11:32">
       <c r="AF14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="11:32">
       <c r="AF15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="11:32">
       <c r="AF16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="32:32">
       <c r="AF17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="32:32">
       <c r="AF18" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="32:32">
       <c r="AF19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="32:32">
       <c r="AF20" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="32:32">
       <c r="AF21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="32:32">
       <c r="AF22" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="32:32">
       <c r="AF23" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24" spans="32:32">
       <c r="AF24" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="32:32">
       <c r="AF25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="32:32">
       <c r="AF26" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="27" spans="32:32">
       <c r="AF27" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="32:32">
       <c r="AF28" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="32:32">
       <c r="AF29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="30" spans="32:32">
       <c r="AF30" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="31" spans="32:32">
       <c r="AF31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="32:32">
       <c r="AF32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="32:32">
       <c r="AF33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="32:32">
       <c r="AF34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="32:32">
       <c r="AF35" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="32:32">
       <c r="AF36" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" spans="32:32">
       <c r="AF37" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="32:32">
       <c r="AF38" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="39" spans="32:32">
       <c r="AF39" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" spans="32:32">
       <c r="AF40" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="32:32">
       <c r="AF41" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" spans="32:32">
       <c r="AF42" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="43" spans="32:32">
       <c r="AF43" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="32:32">
       <c r="AF44" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" spans="32:32">
       <c r="AF45" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="46" spans="32:32">
       <c r="AF46" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" spans="32:32">
       <c r="AF47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="32:32">
       <c r="AF48" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="32:32">
       <c r="AF49" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="32:32">
       <c r="AF50" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="32:32">
       <c r="AF51" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="32:32">
       <c r="AF52" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="53" spans="32:32">
       <c r="AF53" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54" spans="32:32">
       <c r="AF54" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" spans="32:32">
       <c r="AF55" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="56" spans="32:32">
       <c r="AF56" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" spans="32:32">
       <c r="AF57" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="58" spans="32:32">
       <c r="AF58" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" spans="32:32">
       <c r="AF59" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60" spans="32:32">
       <c r="AF60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" spans="32:32">
       <c r="AF61" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="62" spans="32:32">
       <c r="AF62" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="63" spans="32:32">
       <c r="AF63" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="64" spans="32:32">
       <c r="AF64" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="32:32">
       <c r="AF65" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" spans="32:32">
       <c r="AF66" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="67" spans="32:32">
       <c r="AF67" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="68" spans="32:32">
       <c r="AF68" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="69" spans="32:32">
       <c r="AF69" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70" spans="32:32">
       <c r="AF70" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="71" spans="32:32">
       <c r="AF71" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="72" spans="32:32">
       <c r="AF72" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="73" spans="32:32">
       <c r="AF73" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="74" spans="32:32">
       <c r="AF74" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="75" spans="32:32">
       <c r="AF75" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="76" spans="32:32">
       <c r="AF76" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="32:32">
       <c r="AF77" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="78" spans="32:32">
       <c r="AF78" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="79" spans="32:32">
       <c r="AF79" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="80" spans="32:32">
       <c r="AF80" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="32:32">
       <c r="AF81" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="82" spans="32:32">
       <c r="AF82" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="83" spans="32:32">
       <c r="AF83" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="84" spans="32:32">
       <c r="AF84" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="85" spans="32:32">
       <c r="AF85" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="86" spans="32:32">
       <c r="AF86" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="32:32">
       <c r="AF87" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="88" spans="32:32">
       <c r="AF88" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="32:32">
       <c r="AF89" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="32:32">
       <c r="AF90" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="32:32">
       <c r="AF91" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="32:32">
       <c r="AF92" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="93" spans="32:32">
       <c r="AF93" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" spans="32:32">
       <c r="AF94" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="95" spans="32:32">
       <c r="AF95" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="96" spans="32:32">
       <c r="AF96" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="97" spans="32:32">
       <c r="AF97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="32:32">
       <c r="AF98" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="99" spans="32:32">
       <c r="AF99" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="32:32">
       <c r="AF100" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="101" spans="32:32">
       <c r="AF101" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="102" spans="32:32">
       <c r="AF102" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="103" spans="32:32">
       <c r="AF103" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="104" spans="32:32">
       <c r="AF104" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="105" spans="32:32">
       <c r="AF105" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="106" spans="32:32">
       <c r="AF106" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="107" spans="32:32">
       <c r="AF107" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="108" spans="32:32">
       <c r="AF108" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="109" spans="32:32">
       <c r="AF109" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="32:32">
       <c r="AF110" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="111" spans="32:32">
       <c r="AF111" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="112" spans="32:32">
       <c r="AF112" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="113" spans="32:32">
       <c r="AF113" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="32:32">
       <c r="AF114" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115" spans="32:32">
       <c r="AF115" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="116" spans="32:32">
       <c r="AF116" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="32:32">
       <c r="AF117" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="118" spans="32:32">
       <c r="AF118" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="119" spans="32:32">
       <c r="AF119" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="120" spans="32:32">
       <c r="AF120" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="121" spans="32:32">
       <c r="AF121" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" spans="32:32">
       <c r="AF122" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="123" spans="32:32">
       <c r="AF123" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="124" spans="32:32">
       <c r="AF124" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="125" spans="32:32">
       <c r="AF125" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="126" spans="32:32">
       <c r="AF126" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="32:32">
       <c r="AF127" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="128" spans="32:32">
       <c r="AF128" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="129" spans="32:32">
       <c r="AF129" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="130" spans="32:32">
       <c r="AF130" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="131" spans="32:32">
       <c r="AF131" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="132" spans="32:32">
       <c r="AF132" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="133" spans="32:32">
       <c r="AF133" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="134" spans="32:32">
       <c r="AF134" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="135" spans="32:32">
       <c r="AF135" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="136" spans="32:32">
       <c r="AF136" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="137" spans="32:32">
       <c r="AF137" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="138" spans="32:32">
       <c r="AF138" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="139" spans="32:32">
       <c r="AF139" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="140" spans="32:32">
       <c r="AF140" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="141" spans="32:32">
       <c r="AF141" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="142" spans="32:32">
       <c r="AF142" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="143" spans="32:32">
       <c r="AF143" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="144" spans="32:32">
       <c r="AF144" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="145" spans="32:32">
       <c r="AF145" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="146" spans="32:32">
       <c r="AF146" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="147" spans="32:32">
       <c r="AF147" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="148" spans="32:32">
       <c r="AF148" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="32:32">
       <c r="AF149" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="150" spans="32:32">
       <c r="AF150" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="32:32">
       <c r="AF151" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="152" spans="32:32">
       <c r="AF152" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="153" spans="32:32">
       <c r="AF153" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="154" spans="32:32">
       <c r="AF154" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="155" spans="32:32">
       <c r="AF155" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="156" spans="32:32">
       <c r="AF156" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="157" spans="32:32">
       <c r="AF157" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="158" spans="32:32">
       <c r="AF158" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="159" spans="32:32">
       <c r="AF159" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="160" spans="32:32">
       <c r="AF160" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="161" spans="32:32">
       <c r="AF161" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="162" spans="32:32">
       <c r="AF162" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="163" spans="32:32">
       <c r="AF163" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="164" spans="32:32">
       <c r="AF164" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="165" spans="32:32">
       <c r="AF165" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="166" spans="32:32">
       <c r="AF166" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="167" spans="32:32">
       <c r="AF167" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="168" spans="32:32">
       <c r="AF168" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="169" spans="32:32">
       <c r="AF169" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="170" spans="32:32">
       <c r="AF170" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="171" spans="32:32">
       <c r="AF171" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="172" spans="32:32">
       <c r="AF172" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="173" spans="32:32">
       <c r="AF173" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="174" spans="32:32">
       <c r="AF174" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="175" spans="32:32">
       <c r="AF175" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="176" spans="32:32">
       <c r="AF176" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="177" spans="32:32">
       <c r="AF177" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="178" spans="32:32">
       <c r="AF178" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="179" spans="32:32">
       <c r="AF179" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="180" spans="32:32">
       <c r="AF180" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="181" spans="32:32">
       <c r="AF181" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="182" spans="32:32">
       <c r="AF182" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="183" spans="32:32">
       <c r="AF183" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="184" spans="32:32">
       <c r="AF184" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="185" spans="32:32">
       <c r="AF185" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="186" spans="32:32">
       <c r="AF186" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="187" spans="32:32">
       <c r="AF187" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="188" spans="32:32">
       <c r="AF188" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="189" spans="32:32">
       <c r="AF189" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="190" spans="32:32">
       <c r="AF190" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="191" spans="32:32">
       <c r="AF191" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="192" spans="32:32">
       <c r="AF192" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="193" spans="32:32">
       <c r="AF193" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="194" spans="32:32">
       <c r="AF194" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="195" spans="32:32">
       <c r="AF195" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="196" spans="32:32">
       <c r="AF196" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="197" spans="32:32">
       <c r="AF197" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="198" spans="32:32">
       <c r="AF198" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="199" spans="32:32">
       <c r="AF199" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="200" spans="32:32">
       <c r="AF200" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="201" spans="32:32">
       <c r="AF201" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="202" spans="32:32">
       <c r="AF202" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="203" spans="32:32">
       <c r="AF203" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="204" spans="32:32">
       <c r="AF204" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="205" spans="32:32">
       <c r="AF205" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="206" spans="32:32">
       <c r="AF206" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="207" spans="32:32">
       <c r="AF207" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="208" spans="32:32">
       <c r="AF208" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="209" spans="32:32">
       <c r="AF209" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="210" spans="32:32">
       <c r="AF210" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="211" spans="32:32">
       <c r="AF211" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="212" spans="32:32">
       <c r="AF212" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="213" spans="32:32">
       <c r="AF213" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="214" spans="32:32">
       <c r="AF214" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="215" spans="32:32">
       <c r="AF215" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="216" spans="32:32">
       <c r="AF216" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="217" spans="32:32">
       <c r="AF217" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="218" spans="32:32">
       <c r="AF218" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="219" spans="32:32">
       <c r="AF219" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="220" spans="32:32">
       <c r="AF220" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="221" spans="32:32">
       <c r="AF221" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="222" spans="32:32">
       <c r="AF222" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="223" spans="32:32">
       <c r="AF223" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="224" spans="32:32">
       <c r="AF224" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="225" spans="32:32">
       <c r="AF225" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="226" spans="32:32">
       <c r="AF226" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="227" spans="32:32">
       <c r="AF227" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="228" spans="32:32">
       <c r="AF228" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="229" spans="32:32">
       <c r="AF229" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="230" spans="32:32">
       <c r="AF230" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="231" spans="32:32">
       <c r="AF231" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="232" spans="32:32">
       <c r="AF232" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="233" spans="32:32">
       <c r="AF233" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="234" spans="32:32">
       <c r="AF234" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="235" spans="32:32">
       <c r="AF235" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="236" spans="32:32">
       <c r="AF236" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="237" spans="32:32">
       <c r="AF237" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="238" spans="32:32">
       <c r="AF238" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="239" spans="32:32">
       <c r="AF239" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="240" spans="32:32">
       <c r="AF240" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="241" spans="32:32">
       <c r="AF241" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="242" spans="32:32">
       <c r="AF242" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="243" spans="32:32">
       <c r="AF243" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="244" spans="32:32">
       <c r="AF244" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="245" spans="32:32">
       <c r="AF245" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="246" spans="32:32">
       <c r="AF246" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="247" spans="32:32">
       <c r="AF247" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="248" spans="32:32">
       <c r="AF248" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="249" spans="32:32">
       <c r="AF249" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="250" spans="32:32">
       <c r="AF250" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="251" spans="32:32">
       <c r="AF251" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="252" spans="32:32">
       <c r="AF252" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="253" spans="32:32">
       <c r="AF253" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="254" spans="32:32">
       <c r="AF254" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="255" spans="32:32">
       <c r="AF255" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="256" spans="32:32">
       <c r="AF256" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="257" spans="32:32">
       <c r="AF257" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="258" spans="32:32">
       <c r="AF258" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="259" spans="32:32">
       <c r="AF259" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="260" spans="32:32">
       <c r="AF260" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="261" spans="32:32">
       <c r="AF261" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="262" spans="32:32">
       <c r="AF262" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="263" spans="32:32">
       <c r="AF263" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="264" spans="32:32">
       <c r="AF264" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="265" spans="32:32">
       <c r="AF265" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="266" spans="32:32">
       <c r="AF266" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="267" spans="32:32">
       <c r="AF267" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="268" spans="32:32">
       <c r="AF268" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="269" spans="32:32">
       <c r="AF269" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="270" spans="32:32">
       <c r="AF270" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="271" spans="32:32">
       <c r="AF271" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="272" spans="32:32">
       <c r="AF272" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="273" spans="32:32">
       <c r="AF273" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="274" spans="32:32">
       <c r="AF274" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="275" spans="32:32">
       <c r="AF275" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="276" spans="32:32">
       <c r="AF276" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="277" spans="32:32">
       <c r="AF277" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="278" spans="32:32">
       <c r="AF278" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="279" spans="32:32">
       <c r="AF279" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="280" spans="32:32">
       <c r="AF280" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="281" spans="32:32">
       <c r="AF281" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="282" spans="32:32">
       <c r="AF282" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="283" spans="32:32">
       <c r="AF283" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="284" spans="32:32">
       <c r="AF284" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="285" spans="32:32">
       <c r="AF285" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="286" spans="32:32">
       <c r="AF286" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="287" spans="32:32">
       <c r="AF287" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="288" spans="32:32">
       <c r="AF288" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="289" spans="32:32">
       <c r="AF289" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="290" spans="32:32">
       <c r="AF290" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="291" spans="32:32">
       <c r="AF291" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="292" spans="32:32">
       <c r="AF292" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="293" spans="32:32">
       <c r="AF293" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="294" spans="32:32">
       <c r="AF294" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
